--- a/output/full_scan/batch_seq7_2026-07-09.xlsx
+++ b/output/full_scan/batch_seq7_2026-07-09.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O126"/>
+  <dimension ref="A1:O127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -527,21 +527,21 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>6666</v>
+        <v>6834</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>羅麗芬-KY</t>
+          <t>天二科技</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>836.1524986223119</v>
+        <v>856.2870800941569</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>44.45</v>
+        <v>130</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -552,16 +552,16 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>63.94828565503399</v>
+        <v>66.19623883422801</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>46.48570427141468</v>
+        <v>46.1806905323797</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.8043022934041402</v>
+        <v>0.2005087103727569</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>0</v>
@@ -570,31 +570,31 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.0131169220491194</v>
+        <v>-0.431569826059988</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>6488</v>
+        <v>6666</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>羅麗芬-KY</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>758.5531669903536</v>
+        <v>836.1524986223119</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1350</v>
+        <v>44.45</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -605,49 +605,49 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>67.26060729788412</v>
+        <v>63.94828565503399</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>26.18868271705543</v>
+        <v>46.48570427141468</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>1.093201533631466</v>
+        <v>0.8043022934041402</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M3" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>21.42085718997347</v>
+        <v>0.0131169220491194</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>6811</v>
+        <v>6488</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>宏碁資訊</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>671.6261016718499</v>
+        <v>758.5531669903536</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>226</v>
+        <v>1350</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,49 +658,49 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>55.58251525612506</v>
+        <v>67.26060729788412</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>16.88018494908995</v>
+        <v>26.18868271705543</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.6064643449490085</v>
+        <v>1.093201533631466</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M4" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.3701010036748053</v>
+        <v>21.42085718997347</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, foreign_buy_3d, obv_uptrend, dealer_buy_3d</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>6505</v>
+        <v>6811</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>台塑化</t>
+          <t>宏碁資訊</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>667.6765152745438</v>
+        <v>671.6261016718499</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>58.8</v>
+        <v>226</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,16 +711,16 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>60.0951439134346</v>
+        <v>55.58251525612506</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>20.0312554598012</v>
+        <v>16.88018494908995</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.780768706667715</v>
+        <v>0.6064643449490085</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>0</v>
@@ -729,31 +729,31 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.4870307493946533</v>
+        <v>0.3701010036748053</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, foreign_buy_3d, obv_uptrend, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>6579</v>
+        <v>6505</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>研揚</t>
+          <t>台塑化</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>660.0519318813801</v>
+        <v>667.6765152745438</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>168</v>
+        <v>58.8</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,13 +764,13 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>55.65079563365513</v>
+        <v>60.0951439134346</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>22.69065321393249</v>
+        <v>20.0312554598012</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.92462148803372</v>
+        <v>0.780768706667715</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>0</v>
@@ -782,7 +782,7 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.7628516720085554</v>
+        <v>0.4870307493946533</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
@@ -792,21 +792,21 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>6672</v>
+        <v>6579</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>騰輝電子-KY</t>
+          <t>研揚</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>658.9820381707417</v>
+        <v>660.0519318813801</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>298</v>
+        <v>168</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,13 +817,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>63.28453909233581</v>
+        <v>55.65079563365513</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>44.9066951524304</v>
+        <v>22.69065321393249</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.4074601068240206</v>
+        <v>0.92462148803372</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>0</v>
@@ -835,7 +835,7 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.9096220653831572</v>
+        <v>0.7628516720085554</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
@@ -845,21 +845,21 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6491</v>
+        <v>6672</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>晶碩</t>
+          <t>騰輝電子-KY</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>658.6183313400281</v>
+        <v>658.9820381707417</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>375</v>
+        <v>298</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,13 +870,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>76.60579562104009</v>
+        <v>63.28453909233581</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>37.60879281485443</v>
+        <v>44.9066951524304</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.6618331340028111</v>
+        <v>0.4074601068240206</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>4.318203374826927</v>
+        <v>0.9096220653831572</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>6790</v>
+        <v>6491</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>永豐實</t>
+          <t>晶碩</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>657.5848642475654</v>
+        <v>658.6183313400281</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>40.6</v>
+        <v>375</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,13 +923,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>56.06017062060653</v>
+        <v>76.60579562104009</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>27.42534159963564</v>
+        <v>37.60879281485443</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>2.216894408836775</v>
+        <v>0.6618331340028111</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.020065051820983</v>
+        <v>4.318203374826927</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6577</v>
+        <v>6790</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>勁豐</t>
+          <t>永豐實</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>637.1870415150313</v>
+        <v>657.5848642475654</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>80</v>
+        <v>40.6</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,13 +976,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>62.40379616560769</v>
+        <v>56.06017062060653</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>21.3946194609962</v>
+        <v>27.42534159963564</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1.584188463332009</v>
+        <v>2.216894408836775</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.6951246034944096</v>
+        <v>0.020065051820983</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6494</v>
+        <v>6577</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>九齊</t>
+          <t>勁豐</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>605.6281069906465</v>
+        <v>637.1870415150313</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>80</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,16 +1029,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>54.75708980816103</v>
+        <v>62.40379616560769</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>30.79711057973765</v>
+        <v>21.3946194609962</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.4960974403011379</v>
+        <v>1.584188463332009</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>-0.4436447065226803</v>
+        <v>0.6951246034944096</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6548</v>
+        <v>6494</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>長科*</t>
+          <t>九齊</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>605.0684096141974</v>
+        <v>605.6281069906465</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>82.90000000000001</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,49 +1082,49 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>49.3216439275748</v>
+        <v>54.75708980816103</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>35.19220545302394</v>
+        <v>30.79711057973765</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.4280797026316167</v>
+        <v>0.4960974403011379</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M12" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>-1.60683005155984</v>
+        <v>-0.4436447065226803</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, invest_trust_buy_2d, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6719</v>
+        <v>6548</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>力智</t>
+          <t>長科*</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>600.4071475628472</v>
+        <v>605.0684096141974</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>266.5</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,49 +1135,49 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>50.77748287853657</v>
+        <v>49.3216439275748</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>36.36714288232945</v>
+        <v>35.19220545302394</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.4679120686323972</v>
+        <v>0.4280797026316167</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M13" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>-2.178105202216535</v>
+        <v>-1.60683005155984</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, invest_trust_buy_2d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6642</v>
+        <v>6719</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>富致</t>
+          <t>力智</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>598.7544876731299</v>
+        <v>600.4071475628472</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>83</v>
+        <v>266.5</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,16 +1188,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>51.41104344759925</v>
+        <v>50.77748287853657</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>31.20457530042698</v>
+        <v>36.36714288232945</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.6531744208798034</v>
+        <v>0.4679120686323972</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>-0.5639956880125478</v>
+        <v>-2.178105202216535</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6651</v>
+        <v>6642</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>全宇昕</t>
+          <t>富致</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>596.327139434096</v>
+        <v>598.7544876731299</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>153</v>
+        <v>83</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,16 +1241,16 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>52.85462863928228</v>
+        <v>51.41104344759925</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>29.15820875151658</v>
+        <v>31.20457530042698</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.5657071327213851</v>
+        <v>0.6531744208798034</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>-0.3302301955180757</v>
+        <v>-0.5639956880125478</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6538</v>
+        <v>6651</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>倉和</t>
+          <t>全宇昕</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>592.9601059042188</v>
+        <v>596.327139434096</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>136</v>
+        <v>153</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,16 +1294,16 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>59.05258224833558</v>
+        <v>52.85462863928228</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>32.44020151060655</v>
+        <v>29.15820875151658</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.99389783132698</v>
+        <v>0.5657071327213851</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>-0.3265768287639288</v>
+        <v>-0.3302301955180757</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6693</v>
+        <v>6538</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>廣閎科</t>
+          <t>倉和</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>592.7668022939393</v>
+        <v>592.9601059042188</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>236.5</v>
+        <v>136</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,16 +1347,16 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>57.38882725981043</v>
+        <v>59.05258224833558</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>48.35219015072804</v>
+        <v>32.44020151060655</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.7093456386997857</v>
+        <v>0.99389783132698</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>-0.8913554387701943</v>
+        <v>-0.3265768287639288</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>6525</v>
+        <v>6693</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>捷敏-KY</t>
+          <t>廣閎科</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>585.1053716558544</v>
+        <v>592.7668022939393</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>199.5</v>
+        <v>236.5</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,13 +1400,13 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>68.23919948381619</v>
+        <v>57.38882725981043</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>43.6752465029768</v>
+        <v>48.35219015072804</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>1.461046041125038</v>
+        <v>0.7093456386997857</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>4.80468114414046</v>
+        <v>-0.8913554387701943</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6782</v>
+        <v>6525</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>視陽</t>
+          <t>捷敏-KY</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>571.4694015700398</v>
+        <v>585.1053716558544</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>208</v>
+        <v>199.5</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,13 +1453,13 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>61.2161079038716</v>
+        <v>68.23919948381619</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>18.98883099000627</v>
+        <v>43.6752465029768</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1.738489463039223</v>
+        <v>1.461046041125038</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>1.851998813679162</v>
+        <v>4.80468114414046</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>6517</v>
+        <v>6782</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>保勝光學</t>
+          <t>視陽</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>568.6684198466187</v>
+        <v>571.4694015700398</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>65.5</v>
+        <v>208</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,16 +1506,16 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>45.37104325060176</v>
+        <v>61.2161079038716</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>24.30791925562865</v>
+        <v>18.98883099000627</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.1889808519953017</v>
+        <v>1.738489463039223</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>-1.241943777519828</v>
+        <v>1.851998813679162</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6753</v>
+        <v>6517</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>龍德造船</t>
+          <t>保勝光學</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>559.4353987394102</v>
+        <v>568.6684198466187</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>148</v>
+        <v>65.5</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,16 +1559,16 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>62.26465860088243</v>
+        <v>45.37104325060176</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>30.89294198023766</v>
+        <v>24.30791925562865</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>1.502922550900998</v>
+        <v>0.1889808519953017</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>2.721963951680685</v>
+        <v>-1.241943777519828</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>6664</v>
+        <v>6753</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>群翊</t>
+          <t>龍德造船</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>556.9098308629422</v>
+        <v>559.4353987394102</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>373.5</v>
+        <v>148</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,16 +1612,16 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>44.26469167176873</v>
+        <v>62.26465860088243</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>20.06317578971525</v>
+        <v>30.89294198023766</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.5821773104209389</v>
+        <v>1.502922550900998</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>0</v>
@@ -1630,51 +1630,51 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>-0.2885696935309036</v>
+        <v>2.721963951680685</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6806</v>
+        <v>6664</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>森崴能源</t>
+          <t>群翊</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>548.7768356926886</v>
+        <v>556.9098308629422</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>3.51</v>
+        <v>373.5</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G23" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>31.69502785313162</v>
+        <v>44.26469167176873</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>32.59319637267934</v>
+        <v>20.06317578971525</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>2.013053626871306</v>
+        <v>0.5821773104209389</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" s="2" t="n">
         <v>0</v>
@@ -1683,51 +1683,51 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.41128215391912</v>
+        <v>-0.2885696935309036</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6679</v>
+        <v>6806</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>鈺太</t>
+          <t>森崴能源</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>548.6968522564375</v>
+        <v>548.7768356926886</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>249</v>
+        <v>3.51</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G24" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>35.37881367876294</v>
+        <v>31.69502785313162</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>20.18741171691774</v>
+        <v>32.59319637267934</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.4638226669611084</v>
+        <v>2.013053626871306</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>-1.828025668573709</v>
+        <v>0.41128215391912</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6716</v>
+        <v>6679</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>應廣</t>
+          <t>鈺太</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>548.0321698225442</v>
+        <v>548.6968522564375</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>102.5</v>
+        <v>249</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,16 +1771,16 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>57.13843600023346</v>
+        <v>35.37881367876294</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>16.44613674009129</v>
+        <v>20.18741171691774</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>2.082262055376906</v>
+        <v>0.4638226669611084</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.489197438475298</v>
+        <v>-1.828025668573709</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6742</v>
+        <v>6716</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>澤米</t>
+          <t>應廣</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>541.7410460425131</v>
+        <v>548.0321698225442</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>57</v>
+        <v>102.5</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>42.0455364915132</v>
+        <v>57.13843600023346</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>27.90618182887633</v>
+        <v>16.44613674009129</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.2162630642637795</v>
+        <v>2.082262055376906</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>-1.70184001768038</v>
+        <v>0.489197438475298</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6831</v>
+        <v>6742</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>邁科</t>
+          <t>澤米</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>539.9215902987845</v>
+        <v>541.7410460425131</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>782</v>
+        <v>57</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,13 +1877,13 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>48.57509319296665</v>
+        <v>42.0455364915132</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>23.65837690827894</v>
+        <v>27.90618182887633</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.6410763768555681</v>
+        <v>0.2162630642637795</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>0</v>
@@ -1895,7 +1895,7 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>-11.66572969741704</v>
+        <v>-1.70184001768038</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
@@ -1905,21 +1905,21 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6757</v>
+        <v>6831</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>台灣虎航-創</t>
+          <t>邁科</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>539.6201191390852</v>
+        <v>539.9215902987845</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>58.2</v>
+        <v>782</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>47.89947147750377</v>
+        <v>48.57509319296665</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>33.40445402579322</v>
+        <v>23.65837690827894</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.3874529482200982</v>
+        <v>0.6410763768555681</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>-0.5100265763280762</v>
+        <v>-11.66572969741704</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6613</v>
+        <v>6757</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>朋億*</t>
+          <t>台灣虎航-創</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>532.2781759184518</v>
+        <v>539.6201191390852</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>321</v>
+        <v>58.2</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,13 +1983,13 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>48.15488535494868</v>
+        <v>47.89947147750377</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>26.18091667448544</v>
+        <v>33.40445402579322</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.3491639708233205</v>
+        <v>0.3874529482200982</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>-8.294732397570296</v>
+        <v>-0.5100265763280762</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6743</v>
+        <v>6613</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>安普新</t>
+          <t>朋億*</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>519.0535852692602</v>
+        <v>532.2781759184518</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>30.9</v>
+        <v>321</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,13 +2036,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>56.35879887326109</v>
+        <v>48.15488535494868</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>32.54173407440608</v>
+        <v>26.18091667448544</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.3796440245053892</v>
+        <v>0.3491639708233205</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.0066948859906922</v>
+        <v>-8.294732397570296</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6684</v>
+        <v>6743</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>安格</t>
+          <t>安普新</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>513.5871514814752</v>
+        <v>519.0535852692602</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>53.9</v>
+        <v>30.9</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>48.12188770568902</v>
+        <v>56.35879887326109</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>34.74033048301927</v>
+        <v>32.54173407440608</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.2555517275361595</v>
+        <v>0.3796440245053892</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>-0.8440576157012631</v>
+        <v>0.0066948859906922</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6573</v>
+        <v>6684</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>虹揚-KY</t>
+          <t>安格</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>507.9679123019081</v>
+        <v>513.5871514814752</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>27.95</v>
+        <v>53.9</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>73.18948834888442</v>
+        <v>48.12188770568902</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>34.2274652995681</v>
+        <v>34.74033048301927</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>1.396791230190811</v>
+        <v>0.2555517275361595</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.7470358204348275</v>
+        <v>-0.8440576157012631</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6526</v>
+        <v>6573</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>達發</t>
+          <t>虹揚-KY</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>505.8358868881101</v>
+        <v>507.9679123019081</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>652</v>
+        <v>27.95</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,13 +2195,13 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>46.55920798687594</v>
+        <v>73.18948834888442</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>12.50977642032743</v>
+        <v>34.2274652995681</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.3180578006867144</v>
+        <v>1.396791230190811</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>-3.836454092461369</v>
+        <v>0.7470358204348275</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6582</v>
+        <v>6526</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>申豐</t>
+          <t>達發</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>490.9270329656242</v>
+        <v>505.8358868881101</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>32.8</v>
+        <v>652</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>56.37229256984329</v>
+        <v>46.55920798687594</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>35.664471839424</v>
+        <v>12.50977642032743</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.2804601271994546</v>
+        <v>0.3180578006867144</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>-0.0186807447005377</v>
+        <v>-3.836454092461369</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6691</v>
+        <v>6582</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>洋基工程</t>
+          <t>申豐</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>484.1849016766411</v>
+        <v>490.9270329656242</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>708</v>
+        <v>32.8</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,13 +2301,13 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>47.83081935547299</v>
+        <v>56.37229256984329</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>26.21879229894503</v>
+        <v>35.664471839424</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.3184901676641075</v>
+        <v>0.2804601271994546</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-8.401246744581172</v>
+        <v>-0.0186807447005377</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6788</v>
+        <v>6691</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>洋基工程</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>481.9701892520343</v>
+        <v>484.1849016766411</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>403.5</v>
+        <v>708</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,49 +2354,49 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>42.06927030829627</v>
+        <v>47.83081935547299</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>8.618651832724721</v>
+        <v>26.21879229894503</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.4669477995439862</v>
+        <v>0.3184901676641075</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M36" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-3.771028097256124</v>
+        <v>-8.401246744581172</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, invest_trust_buy_2d, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6830</v>
+        <v>6788</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>汎銓</t>
+          <t>華景電</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>472.9114658730273</v>
+        <v>481.9701892520343</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>416.5</v>
+        <v>403.5</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,49 +2407,49 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>31.57675211057729</v>
+        <v>42.06927030829627</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>25.83060348445818</v>
+        <v>8.618651832724721</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.8696450274370079</v>
+        <v>0.4669477995439862</v>
       </c>
       <c r="K37" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L37" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M37" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>-4.110552601916673</v>
+        <v>-3.771028097256124</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6645</v>
+        <v>6830</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>金萬林-創</t>
+          <t>汎銓</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>470.5077411429126</v>
+        <v>472.9114658730273</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>15.8</v>
+        <v>416.5</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,13 +2460,13 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>59.53413654390838</v>
+        <v>31.57675211057729</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>48.60466280454286</v>
+        <v>25.83060348445818</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.4020963480579767</v>
+        <v>0.8696450274370079</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>-0.0835196539687123</v>
+        <v>-4.110552601916673</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6585</v>
+        <v>6645</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>鼎基</t>
+          <t>金萬林-創</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>466.5041939289613</v>
+        <v>470.5077411429126</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>124.5</v>
+        <v>15.8</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>49.89874461129548</v>
+        <v>59.53413654390838</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>39.73939174329298</v>
+        <v>48.60466280454286</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.673118447731708</v>
+        <v>0.4020963480579767</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-2.705165818454747</v>
+        <v>-0.0835196539687123</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6727</v>
+        <v>6585</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>亞泰金屬</t>
+          <t>鼎基</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>464.9460222864213</v>
+        <v>466.5041939289613</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>517</v>
+        <v>124.5</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,13 +2566,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>58.28366804131508</v>
+        <v>49.89874461129548</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>17.45707375504946</v>
+        <v>39.73939174329298</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>1.96396370203577</v>
+        <v>0.673118447731708</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>13.97912698497938</v>
+        <v>-2.705165818454747</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>6794</v>
+        <v>6727</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>向榮生技-創</t>
+          <t>亞泰金屬</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>457.5288297708044</v>
+        <v>464.9460222864213</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>82.40000000000001</v>
+        <v>517</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>55.36983109477574</v>
+        <v>58.28366804131508</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>20.30844591851196</v>
+        <v>17.45707375504946</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.999443721779854</v>
+        <v>1.96396370203577</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>0.5124732337581922</v>
+        <v>13.97912698497938</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6732</v>
+        <v>6794</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>昇佳電子</t>
+          <t>向榮生技-創</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>453.0404578162897</v>
+        <v>457.5288297708044</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>196</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,13 +2672,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>64.86472128421727</v>
+        <v>55.36983109477574</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>24.4352439154899</v>
+        <v>20.30844591851196</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>1.393250363320204</v>
+        <v>0.999443721779854</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>3.999524473965155</v>
+        <v>0.5124732337581922</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6781</v>
+        <v>6732</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>AES-KY</t>
+          <t>昇佳電子</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>450.7193979825053</v>
+        <v>453.0404578162897</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>1130</v>
+        <v>196</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>45.60126260769029</v>
+        <v>64.86472128421727</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>11.61221797963024</v>
+        <v>24.4352439154899</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.5592670369992122</v>
+        <v>1.393250363320204</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-2.427595315825901</v>
+        <v>3.999524473965155</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6739</v>
+        <v>6781</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>竹陞科技</t>
+          <t>AES-KY</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>447.0165362652261</v>
+        <v>450.7193979825053</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>1055</v>
+        <v>1130</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>42.09234324088114</v>
+        <v>45.60126260769029</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>12.21046914747337</v>
+        <v>11.61221797963024</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.799877521461443</v>
+        <v>0.5592670369992122</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,7 +2796,7 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>7.337868287329847</v>
+        <v>-2.427595315825901</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
@@ -2806,21 +2806,21 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6568</v>
+        <v>6739</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>宏觀</t>
+          <t>竹陞科技</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>446.3835646551921</v>
+        <v>447.0165362652261</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>156</v>
+        <v>1055</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,16 +2831,16 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>32.00515919132791</v>
+        <v>42.09234324088114</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>36.85704080117208</v>
+        <v>12.21046914747337</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.5101080921359724</v>
+        <v>0.799877521461443</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="L45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.5733831669263907</v>
+        <v>7.337868287329847</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6560</v>
+        <v>6568</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>欣普羅</t>
+          <t>宏觀</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>445.921869864694</v>
+        <v>446.3835646551921</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>37.6</v>
+        <v>156</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,16 +2884,16 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>43.33677618992704</v>
+        <v>32.00515919132791</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>24.88082843810128</v>
+        <v>36.85704080117208</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.5724180748215562</v>
+        <v>0.5101080921359724</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-0.1358485556437691</v>
+        <v>0.5733831669263907</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6829</v>
+        <v>6560</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>千附精密</t>
+          <t>欣普羅</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>442.0746388788924</v>
+        <v>445.921869864694</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>222</v>
+        <v>37.6</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,16 +2937,16 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>53.37132267543576</v>
+        <v>43.33677618992704</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>12.80794467510524</v>
+        <v>24.88082843810128</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>1.029161936934242</v>
+        <v>0.5724180748215562</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.1342135620633362</v>
+        <v>-0.1358485556437691</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6799</v>
+        <v>6829</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>來頡</t>
+          <t>千附精密</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>434.4648439519448</v>
+        <v>442.0746388788924</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>98.59999999999999</v>
+        <v>222</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,16 +2990,16 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>49.21834816792555</v>
+        <v>53.37132267543576</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>23.06603249237622</v>
+        <v>12.80794467510524</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.6185937495813399</v>
+        <v>1.029161936934242</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-0.0558516872370815</v>
+        <v>0.1342135620633362</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6776</v>
+        <v>6799</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>展碁國際</t>
+          <t>來頡</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>432.1172151615042</v>
+        <v>434.4648439519448</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>55.7</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,13 +3043,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>44.07719399712131</v>
+        <v>49.21834816792555</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>15.1672850214937</v>
+        <v>23.06603249237622</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.4556270969896387</v>
+        <v>0.6185937495813399</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0.007830528605297499</v>
+        <v>-0.0558516872370815</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6534</v>
+        <v>6776</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>正瀚-創</t>
+          <t>展碁國際</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>426.5304830346231</v>
+        <v>432.1172151615042</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>93</v>
+        <v>55.7</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>56.37768592984418</v>
+        <v>44.07719399712131</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>15.95026664238751</v>
+        <v>15.1672850214937</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>1.365323079628226</v>
+        <v>0.4556270969896387</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>0.3359677804539432</v>
+        <v>0.007830528605297499</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6556</v>
+        <v>6534</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>勝品</t>
+          <t>正瀚-創</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>422.7912947879957</v>
+        <v>426.5304830346231</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>70.59999999999999</v>
+        <v>93</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>43.50049536361325</v>
+        <v>56.37768592984418</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>25.41753889866592</v>
+        <v>15.95026664238751</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>4.507926746338204</v>
+        <v>1.365323079628226</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-0.1935381671941433</v>
+        <v>0.3359677804539432</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6668</v>
+        <v>6556</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>中揚光</t>
+          <t>勝品</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>419.0954600328597</v>
+        <v>422.7912947879957</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>37.9</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>44.24061600837763</v>
+        <v>43.50049536361325</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>17.4963482429951</v>
+        <v>25.41753889866592</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.2315904586944201</v>
+        <v>4.507926746338204</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>-0.5166812947517786</v>
+        <v>-0.1935381671941433</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6624</v>
+        <v>6668</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>萬年清</t>
+          <t>中揚光</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>414.3684852514762</v>
+        <v>419.0954600328597</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>40.6</v>
+        <v>37.9</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>50.29260317567155</v>
+        <v>44.24061600837763</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>8.505973094474772</v>
+        <v>17.4963482429951</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.0368485251476237</v>
+        <v>0.2315904586944201</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.9974358011602606</v>
+        <v>-0.5166812947517786</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6669</v>
+        <v>6624</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>萬年清</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>412.5850277970981</v>
+        <v>414.3684852514762</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>5040</v>
+        <v>40.6</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>51.96524514821129</v>
+        <v>50.29260317567155</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>13.1660185490881</v>
+        <v>8.505973094474772</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>1.213334841240199</v>
+        <v>0.0368485251476237</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>35.82695697358312</v>
+        <v>0.9974358011602606</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6654</v>
+        <v>6669</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>天正國際</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>408.2993203541573</v>
+        <v>412.5850277970981</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>187</v>
+        <v>5040</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>53.61942083425149</v>
+        <v>51.96524514821129</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>43.29089107817274</v>
+        <v>13.1660185490881</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.2707091314686251</v>
+        <v>1.213334841240199</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>-3.198907381337586</v>
+        <v>35.82695697358312</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6735</v>
+        <v>6654</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>美達科技</t>
+          <t>天正國際</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>406.8409550006305</v>
+        <v>408.2993203541573</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>80.09999999999999</v>
+        <v>187</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>32.46102817813792</v>
+        <v>53.61942083425149</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>11.02676686405227</v>
+        <v>43.29089107817274</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.3223277732240715</v>
+        <v>0.2707091314686251</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-0.5001901726760138</v>
+        <v>-3.198907381337586</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6625</v>
+        <v>6735</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>必應</t>
+          <t>美達科技</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>403.5764440332376</v>
+        <v>406.8409550006305</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>78.90000000000001</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,16 +3467,16 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>58.91894067445185</v>
+        <v>32.46102817813792</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>25.78125105435794</v>
+        <v>11.02676686405227</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.5638906215452187</v>
+        <v>0.3223277732240715</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-0.069088437656656</v>
+        <v>-0.5001901726760138</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6698</v>
+        <v>6625</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>旭暉應材</t>
+          <t>必應</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>391.6816951447289</v>
+        <v>403.5764440332376</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>40.05</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>47.98460381776182</v>
+        <v>58.91894067445185</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>29.21031086187934</v>
+        <v>25.78125105435794</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.2556492825080236</v>
+        <v>0.5638906215452187</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-0.6451901145955514</v>
+        <v>-0.069088437656656</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6589</v>
+        <v>6698</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>台康生技</t>
+          <t>旭暉應材</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>389.5361902492111</v>
+        <v>391.6816951447289</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>48.25</v>
+        <v>40.05</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,13 +3573,13 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>53.33308383619006</v>
+        <v>47.98460381776182</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>26.27216111244197</v>
+        <v>29.21031086187934</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.5513667336183232</v>
+        <v>0.2556492825080236</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.2027211153908573</v>
+        <v>-0.6451901145955514</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6805</v>
+        <v>6589</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>台康生技</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>388.2261690857828</v>
+        <v>389.5361902492111</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>1460</v>
+        <v>48.25</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>35.04999475126071</v>
+        <v>53.33308383619006</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>23.31580814309379</v>
+        <v>26.27216111244197</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>1.466381395435663</v>
+        <v>0.5513667336183232</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-27.450162596185</v>
+        <v>0.2027211153908573</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6486</v>
+        <v>6805</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>互動</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>386.4315539908017</v>
+        <v>388.2261690857828</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>83.09999999999999</v>
+        <v>1460</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>54.4658411369188</v>
+        <v>35.04999475126071</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>22.52926448286494</v>
+        <v>23.31580814309379</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.7014900816502103</v>
+        <v>1.466381395435663</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.2434784200193814</v>
+        <v>-27.450162596185</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6641</v>
+        <v>6486</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>基士德-KY</t>
+          <t>互動</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>386.3480499949725</v>
+        <v>386.4315539908017</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>18.55</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>52.15916602187611</v>
+        <v>54.4658411369188</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>21.53463698366145</v>
+        <v>22.52926448286494</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.2348049994972524</v>
+        <v>0.7014900816502103</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.07895439815781941</v>
+        <v>0.2434784200193814</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6725</v>
+        <v>6641</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>矽科宏晟</t>
+          <t>基士德-KY</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>383.5367904348528</v>
+        <v>386.3480499949725</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>305.5</v>
+        <v>18.55</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>43.21693973076976</v>
+        <v>52.15916602187611</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>21.50047520525937</v>
+        <v>21.53463698366145</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.1970419132930303</v>
+        <v>0.2348049994972524</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-3.411320418058653</v>
+        <v>0.07895439815781941</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>6530</v>
+        <v>6725</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>創威</t>
+          <t>矽科宏晟</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>381.8663280777081</v>
+        <v>383.5367904348528</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>83</v>
+        <v>305.5</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>35.42061694931276</v>
+        <v>43.21693973076976</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>22.55340179283978</v>
+        <v>21.50047520525937</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.6051592319693341</v>
+        <v>0.1970419132930303</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-0.1612898037756691</v>
+        <v>-3.411320418058653</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6541</v>
+        <v>6530</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>泰福-KY</t>
+          <t>創威</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>380.788563706419</v>
+        <v>381.8663280777081</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>40.8</v>
+        <v>83</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>50.37825057121334</v>
+        <v>35.42061694931276</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>15.95431463958137</v>
+        <v>22.55340179283978</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.4791819830682827</v>
+        <v>0.6051592319693341</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-0.0515945651685702</v>
+        <v>-0.1612898037756691</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6715</v>
+        <v>6541</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>嘉基</t>
+          <t>泰福-KY</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>375.7961387345421</v>
+        <v>380.788563706419</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>391.5</v>
+        <v>40.8</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>41.02153305558943</v>
+        <v>50.37825057121334</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>17.1650809253293</v>
+        <v>15.95431463958137</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>2.332115911198549</v>
+        <v>0.4791819830682827</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-6.670494944877103</v>
+        <v>-0.0515945651685702</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6840</v>
+        <v>6715</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>東研信超</t>
+          <t>嘉基</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>374.2358551769589</v>
+        <v>375.7961387345421</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>66</v>
+        <v>391.5</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>53.08281449922423</v>
+        <v>41.02153305558943</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>12.9618808326741</v>
+        <v>17.1650809253293</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>1.393861081777177</v>
+        <v>2.332115911198549</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.2863977439551996</v>
+        <v>-6.670494944877103</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6510</v>
+        <v>6840</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>東研信超</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>372.8793682236349</v>
+        <v>374.2358551769589</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>2855</v>
+        <v>66</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,49 +4050,49 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>37.50371690907033</v>
+        <v>53.08281449922423</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>20.50776649163218</v>
+        <v>12.9618808326741</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.6169599725795567</v>
+        <v>1.393861081777177</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L68" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M68" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-53.90204377690364</v>
+        <v>0.2863977439551996</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6640</v>
+        <v>6510</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>均華</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>366.708003289398</v>
+        <v>372.8793682236349</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>995</v>
+        <v>2855</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,49 +4103,49 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>38.78904339572949</v>
+        <v>37.50371690907033</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>19.61234233647645</v>
+        <v>20.50776649163218</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.6161250987838414</v>
+        <v>0.6169599725795567</v>
       </c>
       <c r="K69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L69" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M69" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>2.992810433178605</v>
+        <v>-53.90204377690364</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6588</v>
+        <v>6640</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>東典光電</t>
+          <t>均華</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>365.7707035167654</v>
+        <v>366.708003289398</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>78.90000000000001</v>
+        <v>995</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,16 +4156,16 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>27.44225561695703</v>
+        <v>38.78904339572949</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>21.34932605485472</v>
+        <v>19.61234233647645</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.5217914986181071</v>
+        <v>0.6161250987838414</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-0.6701959010467888</v>
+        <v>2.992810433178605</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6667</v>
+        <v>6588</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>信紘科</t>
+          <t>東典光電</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>363.406867881037</v>
+        <v>365.7707035167654</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>255</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>40.36420618809241</v>
+        <v>27.44225561695703</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>11.25283340915759</v>
+        <v>21.34932605485472</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.326947522433445</v>
+        <v>0.5217914986181071</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-2.097105066512831</v>
+        <v>-0.6701959010467888</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6756</v>
+        <v>6667</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>威鋒電子</t>
+          <t>信紘科</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>358.5706487819775</v>
+        <v>363.406867881037</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>99.7</v>
+        <v>255</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>51.11622396576583</v>
+        <v>40.36420618809241</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>18.43002928538239</v>
+        <v>11.25283340915759</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.719580924508797</v>
+        <v>0.326947522433445</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-0.0941166257649045</v>
+        <v>-2.097105066512831</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6695</v>
+        <v>6756</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>芯鼎</t>
+          <t>威鋒電子</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>354.5040666521084</v>
+        <v>358.5706487819775</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>53.7</v>
+        <v>99.7</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>44.25081255653889</v>
+        <v>51.11622396576583</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>20.01410555014847</v>
+        <v>18.43002928538239</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.2781308503205539</v>
+        <v>0.719580924508797</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-1.002137708570736</v>
+        <v>-0.0941166257649045</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6655</v>
+        <v>6695</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>科定</t>
+          <t>芯鼎</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>348.0064297271271</v>
+        <v>354.5040666521084</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>118</v>
+        <v>53.7</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>49.16143910167061</v>
+        <v>44.25081255653889</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>7.712473402461142</v>
+        <v>20.01410555014847</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>1.804025928489872</v>
+        <v>0.2781308503205539</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>1.218665457238765</v>
+        <v>-1.002137708570736</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6708</v>
+        <v>6655</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>天擎</t>
+          <t>科定</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>347.5436602703954</v>
+        <v>348.0064297271271</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>40.15</v>
+        <v>118</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,16 +4421,16 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>51.28270110020168</v>
+        <v>49.16143910167061</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>16.31678883552156</v>
+        <v>7.712473402461142</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>1.394524880344018</v>
+        <v>1.804025928489872</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-0.0191058582267188</v>
+        <v>1.218665457238765</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>6581</v>
+        <v>6708</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>鋼聯</t>
+          <t>天擎</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>347.4493408512781</v>
+        <v>347.5436602703954</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>106.5</v>
+        <v>40.15</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,16 +4474,16 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>43.64214913228103</v>
+        <v>51.28270110020168</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>11.3479901850995</v>
+        <v>16.31678883552156</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>1.861734772157725</v>
+        <v>1.394524880344018</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-0.0759752291492283</v>
+        <v>-0.0191058582267188</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>6584</v>
+        <v>6581</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>南俊國際</t>
+          <t>鋼聯</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>341.5014138720194</v>
+        <v>347.4493408512781</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>663</v>
+        <v>106.5</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>48.49963352537236</v>
+        <v>43.64214913228103</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>13.68941481014204</v>
+        <v>11.3479901850995</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.250640185268231</v>
+        <v>1.861734772157725</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-1.546796010002559</v>
+        <v>-0.0759752291492283</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6722</v>
+        <v>6584</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>輝創</t>
+          <t>南俊國際</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>339.7704691092051</v>
+        <v>341.5014138720194</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>35.45</v>
+        <v>663</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>41.78422609409689</v>
+        <v>48.49963352537236</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>36.62133997578329</v>
+        <v>13.68941481014204</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.1865728134092482</v>
+        <v>0.250640185268231</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.0319693210013282</v>
+        <v>-1.546796010002559</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>6771</v>
+        <v>6722</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>平和環保-創</t>
+          <t>輝創</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>335.9485006770078</v>
+        <v>339.7704691092051</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>39.8</v>
+        <v>35.45</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>44.1112148388866</v>
+        <v>41.78422609409689</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>20.97283035628052</v>
+        <v>36.62133997578329</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.3808665749470042</v>
+        <v>0.1865728134092482</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,7 +4651,7 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>0.0462064449747026</v>
+        <v>0.0319693210013282</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
@@ -4661,21 +4661,21 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>6614</v>
+        <v>6771</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>資拓宏宇</t>
+          <t>平和環保-創</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>332.1724104726767</v>
+        <v>335.9485006770078</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>40</v>
+        <v>39.8</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>49.11212062816623</v>
+        <v>44.1112148388866</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>20.77426728321672</v>
+        <v>20.97283035628052</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.4194081595047057</v>
+        <v>0.3808665749470042</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>0.0148271300024765</v>
+        <v>0.0462064449747026</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>6770</v>
+        <v>6614</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>資拓宏宇</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>330.4379552375836</v>
+        <v>332.1724104726767</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>71.09999999999999</v>
+        <v>40</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>46.51360183865524</v>
+        <v>49.11212062816623</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>17.16066617818829</v>
+        <v>20.77426728321672</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.6783914785034496</v>
+        <v>0.4194081595047057</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-1.255069642368554</v>
+        <v>0.0148271300024765</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>6658</v>
+        <v>6770</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>聯策</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>306.2810580083481</v>
+        <v>330.4379552375836</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>179.5</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>42.72182022624174</v>
+        <v>46.51360183865524</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>23.74112169738468</v>
+        <v>17.16066617818829</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.9127745972555924</v>
+        <v>0.6783914785034496</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-4.125172185823336</v>
+        <v>-1.255069642368554</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>6515</v>
+        <v>6658</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>聯策</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>301.1627714219665</v>
+        <v>306.2810580083481</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>7765</v>
+        <v>179.5</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>40.32504193134784</v>
+        <v>42.72182022624174</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>15.73228466602259</v>
+        <v>23.74112169738468</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.7537787896570529</v>
+        <v>0.9127745972555924</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-129.3450513119197</v>
+        <v>-4.125172185823336</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>6792</v>
+        <v>6515</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>詠業</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>300.7196771235001</v>
+        <v>301.1627714219665</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>61.7</v>
+        <v>7765</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>41.33368101454595</v>
+        <v>40.32504193134784</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>19.98650759353621</v>
+        <v>15.73228466602259</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.4904762088548507</v>
+        <v>0.7537787896570529</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-0.560243079279067</v>
+        <v>-129.3450513119197</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>6821</v>
+        <v>6792</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>聯寶</t>
+          <t>詠業</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>294.6709704854222</v>
+        <v>300.7196771235001</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>51.6</v>
+        <v>61.7</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>33.58037783764908</v>
+        <v>41.33368101454595</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>16.85543691793646</v>
+        <v>19.98650759353621</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.2326609464513606</v>
+        <v>0.4904762088548507</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-1.539659630622465</v>
+        <v>-0.560243079279067</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>6504</v>
+        <v>6821</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>南六</t>
+          <t>聯寶</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>293.1363339467264</v>
+        <v>294.6709704854222</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>36</v>
+        <v>51.6</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>43.4925053262406</v>
+        <v>33.58037783764908</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>14.16677227278365</v>
+        <v>16.85543691793646</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.5408079349634326</v>
+        <v>0.2326609464513606</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>0.1152682033011751</v>
+        <v>-1.539659630622465</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>6598</v>
+        <v>6504</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>ABC-KY</t>
+          <t>南六</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>286.170001218299</v>
+        <v>293.1363339467264</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>22.85</v>
+        <v>36</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>40.50646624594779</v>
+        <v>43.4925053262406</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>15.74469755350476</v>
+        <v>14.16677227278365</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.2679943096239905</v>
+        <v>0.5408079349634326</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-0.0488682956032888</v>
+        <v>0.1152682033011751</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>6823</v>
+        <v>6598</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>濾能</t>
+          <t>ABC-KY</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>285.8192074796418</v>
+        <v>286.170001218299</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>66.2</v>
+        <v>22.85</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>38.92273476343238</v>
+        <v>40.50646624594779</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>15.08127757059748</v>
+        <v>15.74469755350476</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.6895683299719043</v>
+        <v>0.2679943096239905</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>0.1456141922282876</v>
+        <v>-0.0488682956032888</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>6796</v>
+        <v>6823</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>晉弘</t>
+          <t>濾能</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>284.5319982048787</v>
+        <v>285.8192074796418</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>59.2</v>
+        <v>66.2</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>48.76813216284216</v>
+        <v>38.92273476343238</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>22.06564320097512</v>
+        <v>15.08127757059748</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.9376498127101636</v>
+        <v>0.6895683299719043</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>0.381655109705624</v>
+        <v>0.1456141922282876</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>6606</v>
+        <v>6796</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>建德工業</t>
+          <t>晉弘</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>279.710684780087</v>
+        <v>284.5319982048787</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>25.05</v>
+        <v>59.2</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>46.69532408264269</v>
+        <v>48.76813216284216</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>13.03688376972354</v>
+        <v>22.06564320097512</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.5178732407245416</v>
+        <v>0.9376498127101636</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.0106047876657327</v>
+        <v>0.381655109705624</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>6720</v>
+        <v>6606</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>久昌</t>
+          <t>建德工業</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>278.6817965115297</v>
+        <v>279.710684780087</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>140.5</v>
+        <v>25.05</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>44.19777687320438</v>
+        <v>46.69532408264269</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>22.10298401443308</v>
+        <v>13.03688376972354</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.3567069208864492</v>
+        <v>0.5178732407245416</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.6345178227360093</v>
+        <v>0.0106047876657327</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>6570</v>
+        <v>6720</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>維田</t>
+          <t>久昌</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>277.1518155960308</v>
+        <v>278.6817965115297</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>52.8</v>
+        <v>140.5</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>49.7526103334078</v>
+        <v>44.19777687320438</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>18.1888675532136</v>
+        <v>22.10298401443308</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.3900613075357082</v>
+        <v>0.3567069208864492</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-0.1395235368133979</v>
+        <v>0.6345178227360093</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>6531</v>
+        <v>6570</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>維田</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>273.755448438344</v>
+        <v>277.1518155960308</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>922</v>
+        <v>52.8</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>44.9398925140591</v>
+        <v>49.7526103334078</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>19.70161537019482</v>
+        <v>18.1888675532136</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.6913528299949102</v>
+        <v>0.3900613075357082</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-13.47024695107131</v>
+        <v>-0.1395235368133979</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>6533</v>
+        <v>6531</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>271.019284031169</v>
+        <v>273.755448438344</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>191.5</v>
+        <v>922</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>39.3447855008506</v>
+        <v>44.9398925140591</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>9.453825797997183</v>
+        <v>19.70161537019482</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.4116433795171787</v>
+        <v>0.6913528299949102</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>0.06783734483694551</v>
+        <v>-13.47024695107131</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>6592</v>
+        <v>6533</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>和潤企業</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>269.0768804752871</v>
+        <v>271.019284031169</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>59.4</v>
+        <v>191.5</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>37.27174996187637</v>
+        <v>39.3447855008506</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>26.75495347802769</v>
+        <v>9.453825797997183</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>1.107688047528706</v>
+        <v>0.4116433795171787</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-0.4962869640803922</v>
+        <v>0.06783734483694551</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>6789</v>
+        <v>6592</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>采鈺</t>
+          <t>和潤企業</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>268.5211467168094</v>
+        <v>269.0768804752871</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>515</v>
+        <v>59.4</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>49.29976011625968</v>
+        <v>37.27174996187637</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>11.45613658746094</v>
+        <v>26.75495347802769</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.5078244177819691</v>
+        <v>1.107688047528706</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-0.7010781488968267</v>
+        <v>-0.4962869640803922</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>6561</v>
+        <v>6789</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>是方</t>
+          <t>采鈺</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>266.3219879093637</v>
+        <v>268.5211467168094</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>330.5</v>
+        <v>515</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,16 +5587,16 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>39.09196338881269</v>
+        <v>49.29976011625968</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>20.63001740319667</v>
+        <v>11.45613658746094</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.3129231034568797</v>
+        <v>0.5078244177819691</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-0.1680527530098325</v>
+        <v>-0.7010781488968267</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>6761</v>
+        <v>6561</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>穩得</t>
+          <t>是方</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>265.8147523292832</v>
+        <v>266.3219879093637</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>181</v>
+        <v>330.5</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,16 +5640,16 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>42.6093830120512</v>
+        <v>39.09196338881269</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>12.64427597539331</v>
+        <v>20.63001740319667</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.9961010342967304</v>
+        <v>0.3129231034568797</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-0.9036602854693992</v>
+        <v>-0.1680527530098325</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>6670</v>
+        <v>6761</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>復盛應用</t>
+          <t>穩得</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>265.641793367272</v>
+        <v>265.8147523292832</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>261.5</v>
+        <v>181</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>47.69069852276025</v>
+        <v>42.6093830120512</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>19.30187582463844</v>
+        <v>12.64427597539331</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.3084556471968471</v>
+        <v>0.9961010342967304</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-0.626266794751082</v>
+        <v>-0.9036602854693992</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>6498</v>
+        <v>6670</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>久禾光</t>
+          <t>復盛應用</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>261.1769073280221</v>
+        <v>265.641793367272</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>91.8</v>
+        <v>261.5</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,16 +5746,16 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>41.48827068366163</v>
+        <v>47.69069852276025</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>18.97596250747008</v>
+        <v>19.30187582463844</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.3255869692953529</v>
+        <v>0.3084556471968471</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-0.9173587368704204</v>
+        <v>-0.626266794751082</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>6741</v>
+        <v>6498</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>91APP*-KY</t>
+          <t>久禾光</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>260.1821582725876</v>
+        <v>261.1769073280221</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>60</v>
+        <v>91.8</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,16 +5799,16 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>40.98150287444773</v>
+        <v>41.48827068366163</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>9.099618355048433</v>
+        <v>18.97596250747008</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>1.474235345176557</v>
+        <v>0.3255869692953529</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-0.1252753069862333</v>
+        <v>-0.9173587368704204</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>6763</v>
+        <v>6741</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>綠界科技</t>
+          <t>91APP*-KY</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>257.2888543904212</v>
+        <v>260.1821582725876</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>45.9</v>
+        <v>60</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,16 +5852,16 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>44.24551987226324</v>
+        <v>40.98150287444773</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>14.39063609050188</v>
+        <v>9.099618355048433</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.7669989018105312</v>
+        <v>1.474235345176557</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.150683442986275</v>
+        <v>-0.1252753069862333</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>6605</v>
+        <v>6763</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>帝寶</t>
+          <t>綠界科技</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>255.499487966438</v>
+        <v>257.2888543904212</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>126</v>
+        <v>45.9</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>33.57567602890413</v>
+        <v>44.24551987226324</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>13.53493560536608</v>
+        <v>14.39063609050188</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>2.449948796643803</v>
+        <v>0.7669989018105312</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-1.289102729120522</v>
+        <v>-0.150683442986275</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>6512</v>
+        <v>6605</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>啟發電</t>
+          <t>帝寶</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>254.6604456895</v>
+        <v>255.499487966438</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>20.25</v>
+        <v>126</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>52.23819969018646</v>
+        <v>33.57567602890413</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>8.434207485140645</v>
+        <v>13.53493560536608</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.441555801832234</v>
+        <v>2.449948796643803</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>0.3200060053442046</v>
+        <v>-1.289102729120522</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>6643</v>
+        <v>6512</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>M31</t>
+          <t>啟發電</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>246.7443182003722</v>
+        <v>254.6604456895</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>442</v>
+        <v>20.25</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>35.73910301332627</v>
+        <v>52.23819969018646</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>18.7914595652746</v>
+        <v>8.434207485140645</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>1.104121604883709</v>
+        <v>0.441555801832234</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.1686557521434259</v>
+        <v>0.3200060053442046</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>6803</v>
+        <v>6643</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>崑鼎</t>
+          <t>M31</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>239.9642073391052</v>
+        <v>246.7443182003722</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>274</v>
+        <v>442</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,16 +6064,16 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>28.53793051756372</v>
+        <v>35.73910301332627</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>36.65968897583714</v>
+        <v>18.7914595652746</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.2369421464651919</v>
+        <v>1.104121604883709</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-1.579237518457104</v>
+        <v>-0.1686557521434259</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>6690</v>
+        <v>6803</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>安碁資訊</t>
+          <t>崑鼎</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>239.4332732063192</v>
+        <v>239.9642073391052</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>166.5</v>
+        <v>274</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,16 +6117,16 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>44.63014542089192</v>
+        <v>28.53793051756372</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>14.43662579384633</v>
+        <v>36.65968897583714</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.3219020244547579</v>
+        <v>0.2369421464651919</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-0.3006336228533155</v>
+        <v>-1.579237518457104</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>6532</v>
+        <v>6690</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>瑞耘</t>
+          <t>安碁資訊</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>237.9545737167573</v>
+        <v>239.4332732063192</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>78</v>
+        <v>166.5</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,16 +6170,16 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>31.24913596176788</v>
+        <v>44.63014542089192</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>16.15453997305537</v>
+        <v>14.43662579384633</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.7762651967701159</v>
+        <v>0.3219020244547579</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.9832574007868208</v>
+        <v>-0.3006336228533155</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>6546</v>
+        <v>6532</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>正基</t>
+          <t>瑞耘</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>223.4927247787704</v>
+        <v>237.9545737167573</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>67.59999999999999</v>
+        <v>78</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>40.83189043323112</v>
+        <v>31.24913596176788</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>13.29868805191212</v>
+        <v>16.15453997305537</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.752247196514949</v>
+        <v>0.7762651967701159</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>1</v>
@@ -6241,7 +6241,7 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-0.3719280813374186</v>
+        <v>-0.9832574007868208</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
@@ -6251,21 +6251,21 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>6768</v>
+        <v>6546</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>志強-KY</t>
+          <t>正基</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>216.2708120455608</v>
+        <v>223.4927247787704</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>71.2</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,16 +6276,16 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>26.43697348901966</v>
+        <v>40.83189043323112</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>28.2870270438844</v>
+        <v>13.29868805191212</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.5996688685354499</v>
+        <v>0.752247196514949</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-1.14381343142971</v>
+        <v>-0.3719280813374186</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>6680</v>
+        <v>6768</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>鑫創電子</t>
+          <t>志強-KY</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>215.1806078656739</v>
+        <v>216.2708120455608</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>49.35</v>
+        <v>71.2</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>50.04762780743115</v>
+        <v>26.43697348901966</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>3.979599990881895</v>
+        <v>28.2870270438844</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.0916956364419161</v>
+        <v>0.5996688685354499</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>0.09302350343906959</v>
+        <v>-1.14381343142971</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>6835</v>
+        <v>6680</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>圓裕</t>
+          <t>鑫創電子</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>214.5204088787291</v>
+        <v>215.1806078656739</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>34.35</v>
+        <v>49.35</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>34.32925270989293</v>
+        <v>50.04762780743115</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>25.77345061810469</v>
+        <v>3.979599990881895</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.7828998352280849</v>
+        <v>0.0916956364419161</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-0.0445408594690934</v>
+        <v>0.09302350343906959</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>6706</v>
+        <v>6835</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>惠特</t>
+          <t>圓裕</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>211.5132591317279</v>
+        <v>214.5204088787291</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>139</v>
+        <v>34.35</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>37.54028330683413</v>
+        <v>34.32925270989293</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>16.35562293039006</v>
+        <v>25.77345061810469</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.2773792467241036</v>
+        <v>0.7828998352280849</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-1.519361429098996</v>
+        <v>-0.0445408594690934</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>6550</v>
+        <v>6706</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>北極星藥業-KY</t>
+          <t>惠特</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>206.8925943145946</v>
+        <v>211.5132591317279</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>13</v>
+        <v>139</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>41.30874515337634</v>
+        <v>37.54028330683413</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>20.49689766060369</v>
+        <v>16.35562293039006</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.8866924089041965</v>
+        <v>0.2773792467241036</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>0.1399382496071446</v>
+        <v>-1.519361429098996</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>6597</v>
+        <v>6550</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>立誠</t>
+          <t>北極星藥業-KY</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>206.4787716480553</v>
+        <v>206.8925943145946</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>67.8</v>
+        <v>13</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,16 +6541,16 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>51.52220359861456</v>
+        <v>41.30874515337634</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>14.44164553937698</v>
+        <v>20.49689766060369</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.2217467632214176</v>
+        <v>0.8866924089041965</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L115" s="2" t="n">
         <v>0</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-2.553841087597386</v>
+        <v>0.1399382496071446</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, williams_r_recovery</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>6591</v>
+        <v>6597</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>動力-KY</t>
+          <t>立誠</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>201.8795914127689</v>
+        <v>206.4787716480553</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>49.4</v>
+        <v>67.8</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,16 +6594,16 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>31.54900846982505</v>
+        <v>51.52220359861456</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>22.90409399859548</v>
+        <v>14.44164553937698</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>1.305711264294257</v>
+        <v>0.2217467632214176</v>
       </c>
       <c r="K116" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L116" s="2" t="n">
         <v>0</v>
@@ -6612,31 +6612,31 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-0.4216307769851048</v>
+        <v>-2.553841087597386</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, williams_r_recovery</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>6689</v>
+        <v>6591</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>伊雲谷</t>
+          <t>動力-KY</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>184.0970528510371</v>
+        <v>201.8795914127689</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>63.8</v>
+        <v>49.4</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,13 +6647,13 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>41.37266849370007</v>
+        <v>31.54900846982505</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>15.33572375105693</v>
+        <v>22.90409399859548</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.3667007007287019</v>
+        <v>1.305711264294257</v>
       </c>
       <c r="K117" s="2" t="n">
         <v>0</v>
@@ -6665,31 +6665,31 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>-0.0371268966286248</v>
+        <v>-0.4216307769851048</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>6754</v>
+        <v>6689</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>匯僑設計</t>
+          <t>伊雲谷</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>179.8881303456991</v>
+        <v>184.0970528510371</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>41.5</v>
+        <v>63.8</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,13 +6700,13 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>31.97657399723987</v>
+        <v>41.37266849370007</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>18.93448359888314</v>
+        <v>15.33572375105693</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.5416796400835713</v>
+        <v>0.3667007007287019</v>
       </c>
       <c r="K118" s="2" t="n">
         <v>0</v>
@@ -6718,31 +6718,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>-0.398411469049779</v>
+        <v>-0.0371268966286248</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>6657</v>
+        <v>6754</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>華安</t>
+          <t>匯僑設計</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>176.3577815541773</v>
+        <v>179.8881303456991</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>35.3</v>
+        <v>41.5</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,13 +6753,13 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>43.26029149550806</v>
+        <v>31.97657399723987</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>17.09276660438259</v>
+        <v>18.93448359888314</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.5226253375601738</v>
+        <v>0.5416796400835713</v>
       </c>
       <c r="K119" s="2" t="n">
         <v>0</v>
@@ -6771,31 +6771,31 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>0.1999607567496704</v>
+        <v>-0.398411469049779</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>6671</v>
+        <v>6657</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>三能-KY</t>
+          <t>華安</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>170.4396243587977</v>
+        <v>176.3577815541773</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>24.6</v>
+        <v>35.3</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,13 +6806,13 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>33.09146775288033</v>
+        <v>43.26029149550806</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>29.50746914974185</v>
+        <v>17.09276660438259</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.0497590392409964</v>
+        <v>0.5226253375601738</v>
       </c>
       <c r="K120" s="2" t="n">
         <v>0</v>
@@ -6824,31 +6824,31 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>0.1081590525422119</v>
+        <v>0.1999607567496704</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>6552</v>
+        <v>6671</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>易華電</t>
+          <t>三能-KY</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>150.7910911011637</v>
+        <v>170.4396243587977</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>29.45</v>
+        <v>24.6</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,13 +6859,13 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>45.23529017422943</v>
+        <v>33.09146775288033</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>11.04092159257618</v>
+        <v>29.50746914974185</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.6252321844502756</v>
+        <v>0.0497590392409964</v>
       </c>
       <c r="K121" s="2" t="n">
         <v>0</v>
@@ -6877,31 +6877,31 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>-0.08376396773371179</v>
+        <v>0.1081590525422119</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>6692</v>
+        <v>6552</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>進能服</t>
+          <t>易華電</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>131.6309442467248</v>
+        <v>150.7910911011637</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>25</v>
+        <v>29.45</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,13 +6912,13 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>41.721747022876</v>
+        <v>45.23529017422943</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>12.54193451093085</v>
+        <v>11.04092159257618</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.2419352251399605</v>
+        <v>0.6252321844502756</v>
       </c>
       <c r="K122" s="2" t="n">
         <v>0</v>
@@ -6930,31 +6930,31 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>0.0209835230954973</v>
+        <v>-0.08376396773371179</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>6807</v>
+        <v>6692</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>峰源-KY</t>
+          <t>進能服</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>84.01500854294758</v>
+        <v>131.6309442467248</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>33.35</v>
+        <v>25</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6965,13 +6965,13 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>46.52416899355051</v>
+        <v>41.721747022876</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>13.95221324520809</v>
+        <v>12.54193451093085</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.333634743756815</v>
+        <v>0.2419352251399605</v>
       </c>
       <c r="K123" s="2" t="n">
         <v>0</v>
@@ -6983,7 +6983,7 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>0.0753320359022841</v>
+        <v>0.0209835230954973</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
@@ -6993,21 +6993,21 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>6558</v>
+        <v>6807</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>興能高</t>
+          <t>峰源-KY</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>78.106686065905</v>
+        <v>84.01500854294758</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>29.8</v>
+        <v>33.35</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7018,13 +7018,13 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>46.9458938339604</v>
+        <v>46.52416899355051</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>16.41761494540039</v>
+        <v>13.95221324520809</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.4195210839764871</v>
+        <v>0.333634743756815</v>
       </c>
       <c r="K124" s="2" t="n">
         <v>0</v>
@@ -7036,7 +7036,7 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>0.06608813593429599</v>
+        <v>0.0753320359022841</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
@@ -7046,21 +7046,21 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>6838</v>
+        <v>6558</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>台新藥</t>
+          <t>興能高</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v/>
       </c>
       <c r="D125" s="2" t="n">
-        <v>77.67924165856277</v>
+        <v>78.106686065905</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>24.3</v>
+        <v>29.8</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
@@ -7071,13 +7071,13 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>45.03139655084569</v>
+        <v>46.9458938339604</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>12.74871239995593</v>
+        <v>16.41761494540039</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>0.674281140920425</v>
+        <v>0.4195210839764871</v>
       </c>
       <c r="K125" s="2" t="n">
         <v>0</v>
@@ -7089,7 +7089,7 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>0.1029520869004869</v>
+        <v>0.06608813593429599</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
@@ -7099,52 +7099,105 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
+        <v>6838</v>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>台新藥</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D126" s="2" t="n">
+        <v>77.67924165856277</v>
+      </c>
+      <c r="E126" s="2" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H126" s="2" t="n">
+        <v>45.03139655084569</v>
+      </c>
+      <c r="I126" s="2" t="n">
+        <v>12.74871239995593</v>
+      </c>
+      <c r="J126" s="2" t="n">
+        <v>0.674281140920425</v>
+      </c>
+      <c r="K126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N126" s="2" t="n">
+        <v>0.1029520869004869</v>
+      </c>
+      <c r="O126" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
         <v>6674</v>
       </c>
-      <c r="B126" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
         <is>
           <t>鋐寶科技</t>
         </is>
       </c>
-      <c r="C126" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D126" s="2" t="n">
+      <c r="C127" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D127" s="2" t="n">
         <v>77.37069751944527</v>
       </c>
-      <c r="E126" s="2" t="n">
+      <c r="E127" s="2" t="n">
         <v>16.8</v>
       </c>
-      <c r="F126" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="G126" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H126" s="2" t="n">
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H127" s="2" t="n">
         <v>40.38139187665453</v>
       </c>
-      <c r="I126" s="2" t="n">
+      <c r="I127" s="2" t="n">
         <v>18.13934308357284</v>
       </c>
-      <c r="J126" s="2" t="n">
+      <c r="J127" s="2" t="n">
         <v>0.4983078002169389</v>
       </c>
-      <c r="K126" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L126" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M126" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N126" s="2" t="n">
+      <c r="K127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M127" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N127" s="2" t="n">
         <v>-0.0226857404831003</v>
       </c>
-      <c r="O126" s="2" t="inlineStr">
+      <c r="O127" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase</t>
         </is>

--- a/output/full_scan/batch_seq7_2026-07-09.xlsx
+++ b/output/full_scan/batch_seq7_2026-07-09.xlsx
@@ -527,21 +527,21 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>6834</v>
+        <v>6666</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>天二科技</t>
+          <t>羅麗芬-KY</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>856.2870800941569</v>
+        <v>1006.152498622312</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>130</v>
+        <v>44.45</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -552,16 +552,16 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>66.19623883422801</v>
+        <v>63.94828548636514</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>46.1806905323797</v>
+        <v>46.48570431392664</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.2005087103727569</v>
+        <v>0.8043022934041402</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>0</v>
@@ -570,31 +570,31 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>-0.431569826059988</v>
+        <v>0.0131169220681923</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>6666</v>
+        <v>6491</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>羅麗芬-KY</t>
+          <t>晶碩</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>836.1524986223119</v>
+        <v>968.618331340028</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>44.45</v>
+        <v>375</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -605,16 +605,16 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>63.94828565503399</v>
+        <v>76.60579560663595</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>46.48570427141468</v>
+        <v>37.60879283257452</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.8043022934041402</v>
+        <v>0.6618331340028111</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>0</v>
@@ -623,11 +623,11 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.0131169220491194</v>
+        <v>4.318203374731509</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>758.5531669903536</v>
+        <v>958.5531669903536</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>1350</v>
@@ -658,10 +658,10 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>67.26060729788412</v>
+        <v>67.26060728333545</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>26.18868271705543</v>
+        <v>26.18868265223658</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>1.093201533631466</v>
@@ -676,31 +676,31 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>21.42085718997347</v>
+        <v>21.42085719111833</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>6811</v>
+        <v>6505</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>宏碁資訊</t>
+          <t>台塑化</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>671.6261016718499</v>
+        <v>917.6906984448104</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>226</v>
+        <v>58.8</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,16 +711,16 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>55.58251525612506</v>
+        <v>60.09514388190884</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>16.88018494908995</v>
+        <v>20.03125549771677</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.6064643449490085</v>
+        <v>0.7831372472208239</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>0</v>
@@ -729,31 +729,31 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.3701010036748053</v>
+        <v>0.4870307493087931</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, foreign_buy_3d, obv_uptrend, dealer_buy_3d</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>6505</v>
+        <v>6834</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>台塑化</t>
+          <t>天二科技</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>667.6765152745438</v>
+        <v>916.2870800941567</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>58.8</v>
+        <v>130</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,16 +764,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>60.0951439134346</v>
+        <v>66.19623882425188</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>20.0312554598012</v>
+        <v>46.18069053237971</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.780768706667715</v>
+        <v>0.2005087103727569</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.4870307493946533</v>
+        <v>-0.4315698261458518</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>6579</v>
+        <v>6811</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>研揚</t>
+          <t>宏碁資訊</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>660.0519318813801</v>
+        <v>841.6261016718499</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>168</v>
+        <v>226</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,16 +817,16 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>55.65079563365513</v>
+        <v>55.58251512845904</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>22.69065321393249</v>
+        <v>16.88018496321921</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.92462148803372</v>
+        <v>0.6064643449490085</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>0</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.7628516720085554</v>
+        <v>0.3701010038656141</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, foreign_buy_3d, stronger_than_market, obv_uptrend, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6672</v>
+        <v>6577</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>騰輝電子-KY</t>
+          <t>勁豐</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>658.9820381707417</v>
+        <v>837.1870415150313</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>298</v>
+        <v>80</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,13 +870,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>63.28453909233581</v>
+        <v>62.40379606146536</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>44.9066951524304</v>
+        <v>21.39461946099619</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.4074601068240206</v>
+        <v>1.584188463332009</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.9096220653831572</v>
+        <v>0.6951246034944096</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>6491</v>
+        <v>6579</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>晶碩</t>
+          <t>研揚</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>658.6183313400281</v>
+        <v>830.0519318813801</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>375</v>
+        <v>168</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,13 +923,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>76.60579562104009</v>
+        <v>55.65079568800395</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>37.60879281485443</v>
+        <v>22.69065329718225</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.6618331340028111</v>
+        <v>0.92462148803372</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>4.318203374826927</v>
+        <v>0.7628516712453965</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6790</v>
+        <v>6782</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>永豐實</t>
+          <t>視陽</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>657.5848642475654</v>
+        <v>816.4694015700398</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>40.6</v>
+        <v>208</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,16 +976,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>56.06017062060653</v>
+        <v>61.2161079898446</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>27.42534159963564</v>
+        <v>18.98883101348961</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>2.216894408836775</v>
+        <v>1.738489463039223</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.020065051820983</v>
+        <v>1.851998813488339</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6577</v>
+        <v>6672</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>勁豐</t>
+          <t>騰輝電子-KY</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>637.1870415150313</v>
+        <v>813.9820381707417</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>80</v>
+        <v>298</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,13 +1029,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>62.40379616560769</v>
+        <v>63.28453907555873</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>21.3946194609962</v>
+        <v>44.90669516572874</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1.584188463332009</v>
+        <v>0.4074601068240206</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.6951246034944096</v>
+        <v>0.909622065573938</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6494</v>
+        <v>6790</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>九齊</t>
+          <t>永豐實</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>605.6281069906465</v>
+        <v>797.5848642475654</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>40.6</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,16 +1082,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>54.75708980816103</v>
+        <v>56.06017041130701</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>30.79711057973765</v>
+        <v>27.42534162084732</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.4960974403011379</v>
+        <v>2.216894408836775</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>-0.4436447065226803</v>
+        <v>0.0200650518973029</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6548</v>
+        <v>6525</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>長科*</t>
+          <t>捷敏-KY</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>605.0684096141974</v>
+        <v>785.1053716558544</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>82.90000000000001</v>
+        <v>199.5</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,49 +1135,49 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>49.3216439275748</v>
+        <v>68.23919948125268</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>35.19220545302394</v>
+        <v>43.67524651584005</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.4280797026316167</v>
+        <v>1.461046041125038</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M13" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>-1.60683005155984</v>
+        <v>4.804681144159531</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, invest_trust_buy_2d, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6719</v>
+        <v>6743</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>力智</t>
+          <t>安普新</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>600.4071475628472</v>
+        <v>744.0535852692602</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>266.5</v>
+        <v>30.9</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,16 +1188,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>50.77748287853657</v>
+        <v>56.35879885460665</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>36.36714288232945</v>
+        <v>32.54173408655915</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.4679120686323972</v>
+        <v>0.3796440245053892</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>0</v>
@@ -1206,11 +1206,11 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>-2.178105202216535</v>
+        <v>0.0066948859048335</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>598.7544876731299</v>
+        <v>738.7544876731299</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>83</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>51.41104344759925</v>
+        <v>51.41104345733503</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>31.20457530042698</v>
+        <v>31.20457527591326</v>
       </c>
       <c r="J15" s="2" t="n">
         <v>0.6531744208798034</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>-0.5639956880125478</v>
+        <v>-0.5639956881270149</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6651</v>
+        <v>6538</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>全宇昕</t>
+          <t>倉和</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>596.327139434096</v>
+        <v>732.9601059042188</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>153</v>
+        <v>136</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,16 +1294,16 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>52.85462863928228</v>
+        <v>59.05258225227036</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>29.15820875151658</v>
+        <v>32.4402015253709</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.5657071327213851</v>
+        <v>0.99389783132698</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>-0.3302301955180757</v>
+        <v>-0.3265768287448418</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6538</v>
+        <v>6753</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>倉和</t>
+          <t>龍德造船</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>592.9601059042188</v>
+        <v>729.4353987394102</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,13 +1347,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>59.05258224833558</v>
+        <v>62.26465857858909</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>32.44020151060655</v>
+        <v>30.89294198023766</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.99389783132698</v>
+        <v>1.502922550900998</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>1</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>-0.3265768287639288</v>
+        <v>2.721963951585276</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>6693</v>
+        <v>6716</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>廣閎科</t>
+          <t>應廣</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>592.7668022939393</v>
+        <v>718.0321698225441</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>236.5</v>
+        <v>102.5</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,16 +1400,16 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>57.38882725981043</v>
+        <v>57.13843594569693</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>48.35219015072804</v>
+        <v>16.44613672581164</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.7093456386997857</v>
+        <v>2.082262055376906</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>-0.8913554387701943</v>
+        <v>0.4891974386088635</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6525</v>
+        <v>6573</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>捷敏-KY</t>
+          <t>虹揚-KY</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>585.1053716558544</v>
+        <v>707.9679123019081</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>199.5</v>
+        <v>27.95</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,13 +1453,13 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>68.23919948381619</v>
+        <v>73.18948835100079</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>43.6752465029768</v>
+        <v>34.22746531542838</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1.461046041125038</v>
+        <v>1.396791230190811</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>4.80468114414046</v>
+        <v>0.7470358204348275</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>6782</v>
+        <v>6727</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>視陽</t>
+          <t>亞泰金屬</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>571.4694015700398</v>
+        <v>664.9460222864212</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>208</v>
+        <v>517</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>61.2161079038716</v>
+        <v>58.2836680417685</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>18.98883099000627</v>
+        <v>17.45707375504946</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>1.738489463039223</v>
+        <v>1.96396370203577</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>1.851998813679162</v>
+        <v>13.97912698492208</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6517</v>
+        <v>6742</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>保勝光學</t>
+          <t>澤米</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>568.6684198466187</v>
+        <v>661.7410460425131</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>65.5</v>
+        <v>57</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,13 +1559,13 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>45.37104325060176</v>
+        <v>42.04553645942857</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>24.30791925562865</v>
+        <v>27.90618181305625</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.1889808519953017</v>
+        <v>0.2162630642637795</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>3</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>-1.241943777519828</v>
+        <v>-1.701840017584977</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>6753</v>
+        <v>6732</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>龍德造船</t>
+          <t>昇佳電子</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>559.4353987394102</v>
+        <v>653.0404578162897</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>148</v>
+        <v>196</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,13 +1612,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>62.26465860088243</v>
+        <v>64.86472122061869</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>30.89294198023766</v>
+        <v>24.43524384703154</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>1.502922550900998</v>
+        <v>1.393250363320204</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>2.721963951680685</v>
+        <v>3.999524474060566</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6664</v>
+        <v>6831</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>群翊</t>
+          <t>邁科</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>556.9098308629422</v>
+        <v>634.9215902987845</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>373.5</v>
+        <v>782</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,69 +1665,69 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>44.26469167176873</v>
+        <v>48.57509319154209</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>20.06317578971525</v>
+        <v>23.65837691480888</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.5821773104209389</v>
+        <v>0.6410763768555681</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M23" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>-0.2885696935309036</v>
+        <v>-11.66572969743598</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6806</v>
+        <v>6582</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>森崴能源</t>
+          <t>申豐</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>548.7768356926886</v>
+        <v>630.9270329656242</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>3.51</v>
+        <v>32.8</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G24" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>31.69502785313162</v>
+        <v>56.372292646949</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>32.59319637267934</v>
+        <v>35.66447194352689</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>2.013053626871306</v>
+        <v>0.2804601271994546</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.41128215391912</v>
+        <v>-0.0186807447386954</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6679</v>
+        <v>6645</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>鈺太</t>
+          <t>金萬林-創</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>548.6968522564375</v>
+        <v>630.5077411429126</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>249</v>
+        <v>15.8</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,16 +1771,16 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>35.37881367876294</v>
+        <v>59.53413664589409</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>20.18741171691774</v>
+        <v>48.60466284566979</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.4638226669611084</v>
+        <v>0.4020963480579767</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>-1.828025668573709</v>
+        <v>-0.0835196540736501</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6716</v>
+        <v>6794</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>應廣</t>
+          <t>向榮生技-創</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>548.0321698225442</v>
+        <v>627.5288297708042</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>102.5</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,13 +1824,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>57.13843600023346</v>
+        <v>55.36983105474208</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>16.44613674009129</v>
+        <v>20.30844591851196</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>2.082262055376906</v>
+        <v>0.999443721779854</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>1</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>0.489197438475298</v>
+        <v>0.512473233834514</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6742</v>
+        <v>6526</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>澤米</t>
+          <t>達發</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>541.7410460425131</v>
+        <v>620.8358868881099</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>57</v>
+        <v>652</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,49 +1877,49 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>42.0455364915132</v>
+        <v>46.55920794044477</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>27.90618182887633</v>
+        <v>12.50977640156015</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.2162630642637795</v>
+        <v>0.3180578006867144</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="M27" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>-1.70184001768038</v>
+        <v>-3.836454092270575</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6831</v>
+        <v>6494</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>邁科</t>
+          <t>九齊</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>539.9215902987845</v>
+        <v>605.6281069906465</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>782</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,16 +1930,16 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>48.57509319296665</v>
+        <v>54.75708981889597</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>23.65837690827894</v>
+        <v>30.79711053846729</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.6410763768555681</v>
+        <v>0.4960974403011379</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>-11.66572969741704</v>
+        <v>-0.4436447065226803</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6757</v>
+        <v>6548</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>台灣虎航-創</t>
+          <t>長科*</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>539.6201191390852</v>
+        <v>605.0684096141974</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>58.2</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,49 +1983,49 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>47.89947147750377</v>
+        <v>49.32164392833502</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>33.40445402579322</v>
+        <v>35.19220546615367</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.3874529482200982</v>
+        <v>0.4280797026316167</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M29" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>-0.5100265763280762</v>
+        <v>-1.606830051550298</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, invest_trust_buy_2d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6613</v>
+        <v>6776</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>朋億*</t>
+          <t>展碁國際</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>532.2781759184518</v>
+        <v>602.1172151615042</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>321</v>
+        <v>55.7</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>48.15488535494868</v>
+        <v>44.07719400615863</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>26.18091667448544</v>
+        <v>15.16728503789413</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.3491639708233205</v>
+        <v>0.4556270969896387</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>-8.294732397570296</v>
+        <v>0.007830528605297499</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6743</v>
+        <v>6719</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>安普新</t>
+          <t>力智</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>519.0535852692602</v>
+        <v>600.4071475628472</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>30.9</v>
+        <v>266.5</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>56.35879887326109</v>
+        <v>50.77748288044828</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>32.54173407440608</v>
+        <v>36.36714290865228</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.3796440245053892</v>
+        <v>0.4679120686323972</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.0066948859906922</v>
+        <v>-2.178105202121177</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6684</v>
+        <v>6534</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>安格</t>
+          <t>正瀚-創</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>513.5871514814752</v>
+        <v>596.5304830346231</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>53.9</v>
+        <v>93</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>48.12188770568902</v>
+        <v>56.377685820084</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>34.74033048301927</v>
+        <v>15.95026664477515</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.2555517275361595</v>
+        <v>1.365323079628226</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>-0.8440576157012631</v>
+        <v>0.3359677804920924</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6573</v>
+        <v>6651</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>虹揚-KY</t>
+          <t>全宇昕</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>507.9679123019081</v>
+        <v>596.327139434096</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>27.95</v>
+        <v>153</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,13 +2195,13 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>73.18948834888442</v>
+        <v>52.85462862539603</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>34.2274652995681</v>
+        <v>29.15820876787029</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>1.396791230190811</v>
+        <v>0.5657071327213851</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.7470358204348275</v>
+        <v>-0.3302301955753322</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6526</v>
+        <v>6693</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>達發</t>
+          <t>廣閎科</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>505.8358868881101</v>
+        <v>592.7668022939393</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>652</v>
+        <v>236.5</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>46.55920798687594</v>
+        <v>57.38882725730897</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>12.50977642032743</v>
+        <v>48.35219013904855</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.3180578006867144</v>
+        <v>0.7093456386997857</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>-3.836454092461369</v>
+        <v>-0.8913554387701943</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6582</v>
+        <v>6829</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>申豐</t>
+          <t>千附精密</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>490.9270329656242</v>
+        <v>582.0746388788924</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>32.8</v>
+        <v>222</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,16 +2301,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>56.37229256984329</v>
+        <v>53.37132264412852</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>35.664471839424</v>
+        <v>12.80794466052242</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.2804601271994546</v>
+        <v>1.029161936934242</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-0.0186807447005377</v>
+        <v>0.134213562158755</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6691</v>
+        <v>6517</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>洋基工程</t>
+          <t>保勝光學</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>484.1849016766411</v>
+        <v>568.6684198466187</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>708</v>
+        <v>65.5</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,16 +2354,16 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>47.83081935547299</v>
+        <v>45.37104323650273</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>26.21879229894503</v>
+        <v>24.30791927159173</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.3184901676641075</v>
+        <v>0.1889808519953017</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-8.401246744581172</v>
+        <v>-1.241943777748783</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6788</v>
+        <v>6589</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>台康生技</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>481.9701892520343</v>
+        <v>559.5361902492111</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>403.5</v>
+        <v>48.25</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,49 +2407,49 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>42.06927030829627</v>
+        <v>53.33308396973563</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>8.618651832724721</v>
+        <v>26.2721611404946</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.4669477995439862</v>
+        <v>0.5513667336183232</v>
       </c>
       <c r="K37" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L37" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M37" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>-3.771028097256124</v>
+        <v>0.2027211153336168</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, invest_trust_buy_2d, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6830</v>
+        <v>6664</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>汎銓</t>
+          <t>群翊</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>472.9114658730273</v>
+        <v>556.9098308629422</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>416.5</v>
+        <v>373.5</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,16 +2460,16 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>31.57675211057729</v>
+        <v>44.26469162260563</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>25.83060348445818</v>
+        <v>20.06317581335328</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.8696450274370079</v>
+        <v>0.5821773104209389</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>0</v>
@@ -2478,48 +2478,48 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>-4.110552601916673</v>
+        <v>-0.2885696932447139</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6645</v>
+        <v>6806</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>金萬林-創</t>
+          <t>森崴能源</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>470.5077411429126</v>
+        <v>548.7768356926886</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>15.8</v>
+        <v>3.51</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G39" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>59.53413654390838</v>
+        <v>31.69502865962096</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>48.60466280454286</v>
+        <v>32.59319664960387</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.4020963480579767</v>
+        <v>2.013053626871306</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-0.0835196539687123</v>
+        <v>0.4112821537115656</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6585</v>
+        <v>6679</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>鼎基</t>
+          <t>鈺太</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>466.5041939289613</v>
+        <v>548.6968522564375</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>124.5</v>
+        <v>249</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,16 +2566,16 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>49.89874461129548</v>
+        <v>35.37881362745074</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>39.73939174329298</v>
+        <v>20.18741173433484</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.673118447731708</v>
+        <v>0.4638226669611084</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>-2.705165818454747</v>
+        <v>-1.828025668382936</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>6727</v>
+        <v>6654</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>亞泰金屬</t>
+          <t>天正國際</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>464.9460222864213</v>
+        <v>548.2993203541573</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>517</v>
+        <v>187</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>58.28366804131508</v>
+        <v>53.61942081852476</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>17.45707375504946</v>
+        <v>43.29089109078677</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>1.96396370203577</v>
+        <v>0.2707091314686251</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>13.97912698497938</v>
+        <v>-3.198907381852711</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6794</v>
+        <v>6840</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>向榮生技-創</t>
+          <t>東研信超</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>457.5288297708044</v>
+        <v>544.2358551769588</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>82.40000000000001</v>
+        <v>66</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,13 +2672,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>55.36983109477574</v>
+        <v>53.08281449683496</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>20.30844591851196</v>
+        <v>12.9618808326741</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.999443721779854</v>
+        <v>1.393861081777177</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.5124732337581922</v>
+        <v>0.2863977439361214</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6732</v>
+        <v>6625</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>昇佳電子</t>
+          <t>必應</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>453.0404578162897</v>
+        <v>543.5764440332375</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>196</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,16 +2725,16 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>64.86472128421727</v>
+        <v>58.91894064313828</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>24.4352439154899</v>
+        <v>25.78125105141108</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>1.393250363320204</v>
+        <v>0.5638906215452187</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>3.999524473965155</v>
+        <v>-0.0690884378283755</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6781</v>
+        <v>6641</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>AES-KY</t>
+          <t>基士德-KY</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>450.7193979825053</v>
+        <v>541.3480499949726</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>1130</v>
+        <v>18.55</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>45.60126260769029</v>
+        <v>52.15916601029208</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>11.61221797963024</v>
+        <v>21.53463700116355</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.5592670369992122</v>
+        <v>0.2348049994972524</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>-2.427595315825901</v>
+        <v>0.0789543981768993</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6739</v>
+        <v>6757</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>竹陞科技</t>
+          <t>台灣虎航-創</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>447.0165362652261</v>
+        <v>539.6201191390852</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>1055</v>
+        <v>58.2</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>42.09234324088114</v>
+        <v>47.89947150532576</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>12.21046914747337</v>
+        <v>33.4044542250839</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.799877521461443</v>
+        <v>0.3874529482200982</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>7.337868287329847</v>
+        <v>-0.510026576499796</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6568</v>
+        <v>6556</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>宏觀</t>
+          <t>勝品</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>446.3835646551921</v>
+        <v>537.7912947879956</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>156</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,16 +2884,16 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>32.00515919132791</v>
+        <v>43.50049532804022</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>36.85704080117208</v>
+        <v>25.4175389739355</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.5101080921359724</v>
+        <v>4.507926746338204</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="L46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.5733831669263907</v>
+        <v>-0.193538167136914</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6560</v>
+        <v>6668</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>欣普羅</t>
+          <t>中揚光</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>445.921869864694</v>
+        <v>534.0954600328597</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>37.6</v>
+        <v>37.9</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,16 +2937,16 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>43.33677618992704</v>
+        <v>44.24061600837763</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>24.88082843810128</v>
+        <v>17.49634825636789</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.5724180748215562</v>
+        <v>0.2315904586944201</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-0.1358485556437691</v>
+        <v>-0.5166812948567168</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6829</v>
+        <v>6613</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>千附精密</t>
+          <t>朋億*</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>442.0746388788924</v>
+        <v>532.2781759184518</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>222</v>
+        <v>321</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,16 +2990,16 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>53.37132267543576</v>
+        <v>48.1548853306832</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>12.80794467510524</v>
+        <v>26.18091668333613</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>1.029161936934242</v>
+        <v>0.3491639708233205</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>0.1342135620633362</v>
+        <v>-8.294732397284093</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6799</v>
+        <v>6669</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>來頡</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>434.4648439519448</v>
+        <v>527.7527193266883</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>98.59999999999999</v>
+        <v>5040</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,49 +3043,49 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>49.21834816792555</v>
+        <v>51.96524510439431</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>23.06603249237622</v>
+        <v>13.16601854784374</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.6185937495813399</v>
+        <v>1.239935985599949</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L49" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M49" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-0.0558516872370815</v>
+        <v>35.82695697358312</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6776</v>
+        <v>6486</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>展碁國際</t>
+          <t>互動</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>432.1172151615042</v>
+        <v>526.4315539908017</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>55.7</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>44.07719399712131</v>
+        <v>54.46584108495598</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>15.1672850214937</v>
+        <v>22.52926446869758</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.4556270969896387</v>
+        <v>0.7014900816502103</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>0.007830528605297499</v>
+        <v>0.2434784200002912</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6534</v>
+        <v>6541</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>正瀚-創</t>
+          <t>泰福-KY</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>426.5304830346231</v>
+        <v>520.788563706419</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>93</v>
+        <v>40.8</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,16 +3149,16 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>56.37768592984418</v>
+        <v>50.37825055393518</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>15.95026664238751</v>
+        <v>15.95431463490334</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>1.365323079628226</v>
+        <v>0.4791819830682827</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>0.3359677804539432</v>
+        <v>-0.0515945649777843</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6556</v>
+        <v>6684</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>勝品</t>
+          <t>安格</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>422.7912947879957</v>
+        <v>513.5871514814752</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>70.59999999999999</v>
+        <v>53.9</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>43.50049536361325</v>
+        <v>48.12188760072574</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>25.41753889866592</v>
+        <v>34.74033046096234</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>4.507926746338204</v>
+        <v>0.2555517275361595</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>-0.1935381671941433</v>
+        <v>-0.844057614690052</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6668</v>
+        <v>6722</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>中揚光</t>
+          <t>輝創</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>419.0954600328597</v>
+        <v>509.7704691092051</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>37.9</v>
+        <v>35.45</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>44.24061600837763</v>
+        <v>41.78422157427065</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>17.4963482429951</v>
+        <v>36.62134005229357</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.2315904586944201</v>
+        <v>0.1865728134092482</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-0.5166812947517786</v>
+        <v>0.0319693211539622</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6624</v>
+        <v>6771</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>萬年清</t>
+          <t>平和環保-創</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>414.3684852514762</v>
+        <v>505.9485006770078</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>40.6</v>
+        <v>39.8</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>50.29260317567155</v>
+        <v>44.11121485010584</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>8.505973094474772</v>
+        <v>20.97283053484768</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.0368485251476237</v>
+        <v>0.3808665749470042</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.9974358011602606</v>
+        <v>0.0462064449937836</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6669</v>
+        <v>6756</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>威鋒電子</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>412.5850277970981</v>
+        <v>498.5706487819775</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>5040</v>
+        <v>99.7</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,16 +3361,16 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>51.96524514821129</v>
+        <v>51.11622393290391</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>13.1660185490881</v>
+        <v>18.43002931375125</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>1.213334841240199</v>
+        <v>0.719580924508797</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>35.82695697358312</v>
+        <v>-0.0941166256695159</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6654</v>
+        <v>6805</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>天正國際</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>408.2993203541573</v>
+        <v>498.2261690857841</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>187</v>
+        <v>1460</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>53.61942083425149</v>
+        <v>35.04999473985863</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>43.29089107817274</v>
+        <v>23.31580815943655</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.2707091314686251</v>
+        <v>1.466381395435663</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-3.198907381337586</v>
+        <v>-27.45016259752049</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6735</v>
+        <v>6530</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>美達科技</t>
+          <t>創威</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>406.8409550006305</v>
+        <v>496.8663280777081</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>80.09999999999999</v>
+        <v>83</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,16 +3467,16 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>32.46102817813792</v>
+        <v>35.42061692529114</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>11.02676686405227</v>
+        <v>22.55340177651775</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.3223277732240715</v>
+        <v>0.6051592319693341</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-0.5001901726760138</v>
+        <v>-0.1612898038329095</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6625</v>
+        <v>6708</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>必應</t>
+          <t>天擎</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>403.5764440332376</v>
+        <v>487.5436602703954</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>78.90000000000001</v>
+        <v>40.15</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,16 +3520,16 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>58.91894067445185</v>
+        <v>51.28270097937289</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>25.78125105435794</v>
+        <v>16.31678885415651</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.5638906215452187</v>
+        <v>1.394524880344018</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-0.069088437656656</v>
+        <v>-0.0191058580550038</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6698</v>
+        <v>6581</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>旭暉應材</t>
+          <t>鋼聯</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>391.6816951447289</v>
+        <v>487.4493408512781</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>40.05</v>
+        <v>106.5</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>47.98460381776182</v>
+        <v>43.64214916955456</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>29.21031086187934</v>
+        <v>11.34799022438651</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.2556492825080236</v>
+        <v>1.861734772157725</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-0.6451901145955514</v>
+        <v>-0.0759752293400259</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6589</v>
+        <v>6691</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>台康生技</t>
+          <t>洋基工程</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>389.5361902492111</v>
+        <v>484.1849016766411</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>48.25</v>
+        <v>708</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>53.33308383619006</v>
+        <v>47.83081928113256</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>26.27216111244197</v>
+        <v>26.21879230494516</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.5513667336183232</v>
+        <v>0.3184901676641075</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.2027211153908573</v>
+        <v>-8.401246741242378</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6805</v>
+        <v>6830</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>汎銓</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>388.2261690857828</v>
+        <v>482.9114658730273</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>1460</v>
+        <v>416.5</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>35.04999475126071</v>
+        <v>31.57675210294522</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>23.31580814309379</v>
+        <v>25.83060349809814</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>1.466381395435663</v>
+        <v>0.8696450274370079</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-27.450162596185</v>
+        <v>-4.110552602012078</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6486</v>
+        <v>6788</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>互動</t>
+          <t>華景電</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>386.4315539908017</v>
+        <v>481.9701892520345</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>83.09999999999999</v>
+        <v>403.5</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,49 +3732,49 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>54.4658411369188</v>
+        <v>42.06927033991832</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>22.52926448286494</v>
+        <v>8.618651842756288</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.7014900816502103</v>
+        <v>0.4669477995439862</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L62" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M62" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.2434784200193814</v>
+        <v>-3.771028098114664</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6641</v>
+        <v>6614</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>基士德-KY</t>
+          <t>資拓宏宇</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>386.3480499949725</v>
+        <v>472.1724104726767</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>18.55</v>
+        <v>40</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,16 +3785,16 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>52.15916602187611</v>
+        <v>49.11212072275216</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>21.53463698366145</v>
+        <v>20.77426729531906</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.2348049994972524</v>
+        <v>0.4194081595047057</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.07895439815781941</v>
+        <v>0.0148271299643166</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>6725</v>
+        <v>6655</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>矽科宏晟</t>
+          <t>科定</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>383.5367904348528</v>
+        <v>463.0064297271271</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>305.5</v>
+        <v>118</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>43.21693973076976</v>
+        <v>49.16143910167061</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>21.50047520525937</v>
+        <v>7.71247340138092</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.1970419132930303</v>
+        <v>1.804025928489872</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-3.411320418058653</v>
+        <v>1.218665457238765</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6530</v>
+        <v>6585</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>創威</t>
+          <t>鼎基</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>381.8663280777081</v>
+        <v>456.5041939289613</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>83</v>
+        <v>124.5</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>35.42061694931276</v>
+        <v>49.89874454587265</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>22.55340179283978</v>
+        <v>39.73939175613441</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.6051592319693341</v>
+        <v>0.673118447731708</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-0.1612898037756691</v>
+        <v>-2.705165818168562</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6541</v>
+        <v>6512</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>泰福-KY</t>
+          <t>啟發電</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>380.788563706419</v>
+        <v>454.6604456894999</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>40.8</v>
+        <v>20.25</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>50.37825057121334</v>
+        <v>52.23819969334869</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>15.95431463958137</v>
+        <v>8.434207490644807</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.4791819830682827</v>
+        <v>0.441555801832234</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-0.0515945651685702</v>
+        <v>0.3200060053060451</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6715</v>
+        <v>6781</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>嘉基</t>
+          <t>AES-KY</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>375.7961387345421</v>
+        <v>450.7193979825053</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>391.5</v>
+        <v>1130</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>41.02153305558943</v>
+        <v>45.60126261155782</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>17.1650809253293</v>
+        <v>11.61221803990952</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>2.332115911198549</v>
+        <v>0.5592670369992122</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-6.670494944877103</v>
+        <v>-2.427595318496987</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6840</v>
+        <v>6739</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>東研信超</t>
+          <t>竹陞科技</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>374.2358551769589</v>
+        <v>447.0165362652241</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>66</v>
+        <v>1055</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>53.08281449922423</v>
+        <v>42.0923432350861</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>12.9618808326741</v>
+        <v>12.21046922174991</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>1.393861081777177</v>
+        <v>0.799877521461443</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.2863977439551996</v>
+        <v>7.337868287234389</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6510</v>
+        <v>6568</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>宏觀</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>372.8793682236349</v>
+        <v>446.3835646551921</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>2855</v>
+        <v>156</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,49 +4103,49 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>37.50371690907033</v>
+        <v>32.00515919501437</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>20.50776649163218</v>
+        <v>36.85704086129769</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.6169599725795567</v>
+        <v>0.5101080921359724</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L69" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M69" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-53.90204377690364</v>
+        <v>0.5733831665447742</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6640</v>
+        <v>6560</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>均華</t>
+          <t>欣普羅</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>366.708003289398</v>
+        <v>445.921869864694</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>995</v>
+        <v>37.6</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,16 +4156,16 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>38.78904339572949</v>
+        <v>43.33677628827902</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>19.61234233647645</v>
+        <v>24.88082841535185</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.6161250987838414</v>
+        <v>0.5724180748215562</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>2.992810433178605</v>
+        <v>-0.1358485556819243</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6588</v>
+        <v>6670</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>東典光電</t>
+          <t>復盛應用</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>365.7707035167654</v>
+        <v>445.6417933672719</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>78.90000000000001</v>
+        <v>261.5</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,16 +4209,16 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>27.44225561695703</v>
+        <v>47.69069867348944</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>21.34932605485472</v>
+        <v>19.3018759365178</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.5217914986181071</v>
+        <v>0.3084556471968471</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-0.6701959010467888</v>
+        <v>-0.6262667939879174</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6667</v>
+        <v>6504</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>信紘科</t>
+          <t>南六</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>363.406867881037</v>
+        <v>433.1363339467263</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>255</v>
+        <v>36</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>40.36420618809241</v>
+        <v>43.49250602270006</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>11.25283340915759</v>
+        <v>14.16677240282557</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.326947522433445</v>
+        <v>0.5408079349634326</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-2.097105066512831</v>
+        <v>0.1152682032248567</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6756</v>
+        <v>6598</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>威鋒電子</t>
+          <t>ABC-KY</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>358.5706487819775</v>
+        <v>426.1700012182991</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>99.7</v>
+        <v>22.85</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>51.11622396576583</v>
+        <v>40.5064664471039</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>18.43002928538239</v>
+        <v>15.74469751919736</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.719580924508797</v>
+        <v>0.2679943096239905</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-0.0941166257649045</v>
+        <v>-0.0488682955555953</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6695</v>
+        <v>6796</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>芯鼎</t>
+          <t>晉弘</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>354.5040666521084</v>
+        <v>424.5319982048787</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>53.7</v>
+        <v>59.2</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,16 +4368,16 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>44.25081255653889</v>
+        <v>48.76813210429393</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>20.01410555014847</v>
+        <v>22.0656432129001</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.2781308503205539</v>
+        <v>0.9376498127101636</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-1.002137708570736</v>
+        <v>0.3816551098582617</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6655</v>
+        <v>6799</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>科定</t>
+          <t>來頡</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>348.0064297271271</v>
+        <v>424.4648439519449</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>118</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>49.16143910167061</v>
+        <v>49.21834808672387</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>7.712473402461142</v>
+        <v>23.06603249237622</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>1.804025928489872</v>
+        <v>0.6185937495813399</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>1.218665457238765</v>
+        <v>-0.0558516872370815</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>6708</v>
+        <v>6606</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>天擎</t>
+          <t>建德工業</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>347.5436602703954</v>
+        <v>419.710684780087</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>40.15</v>
+        <v>25.05</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,16 +4474,16 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>51.28270110020168</v>
+        <v>46.69532413206141</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>16.31678883552156</v>
+        <v>13.03688383720157</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>1.394524880344018</v>
+        <v>0.5178732407245416</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-0.0191058582267188</v>
+        <v>0.0106047876275759</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>6581</v>
+        <v>6658</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>鋼聯</t>
+          <t>聯策</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>347.4493408512781</v>
+        <v>416.2810580083481</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>106.5</v>
+        <v>179.5</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,16 +4527,16 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>43.64214913228103</v>
+        <v>42.7218202355799</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>11.3479901850995</v>
+        <v>23.74112172763247</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>1.861734772157725</v>
+        <v>0.9127745972555924</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-0.0759752291492283</v>
+        <v>-4.125172186281256</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6584</v>
+        <v>6624</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>南俊國際</t>
+          <t>萬年清</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>341.5014138720194</v>
+        <v>414.3684852514762</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>663</v>
+        <v>40.6</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>48.49963352537236</v>
+        <v>50.29260317881331</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>13.68941481014204</v>
+        <v>8.505973106037118</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.250640185268231</v>
+        <v>0.0368485251476237</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-1.546796010002559</v>
+        <v>0.9974358010648676</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>6722</v>
+        <v>6592</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>輝創</t>
+          <t>和潤企業</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>339.7704691092051</v>
+        <v>409.0768804752871</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>35.45</v>
+        <v>59.4</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>41.78422609409689</v>
+        <v>37.27174990214328</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>36.62133997578329</v>
+        <v>26.75495347802769</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.1865728134092482</v>
+        <v>1.107688047528706</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>0.0319693210013282</v>
+        <v>-0.4962869640613102</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>6771</v>
+        <v>6735</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>平和環保-創</t>
+          <t>美達科技</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>335.9485006770078</v>
+        <v>406.8409550006305</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>39.8</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,16 +4686,16 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>44.1112148388866</v>
+        <v>32.4610281619691</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>20.97283035628052</v>
+        <v>11.02676687045404</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.3808665749470042</v>
+        <v>0.3223277732240715</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>0.0462064449747026</v>
+        <v>-0.5001901727714104</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>6614</v>
+        <v>6570</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>資拓宏宇</t>
+          <t>維田</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>332.1724104726767</v>
+        <v>392.1518155960307</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>40</v>
+        <v>52.8</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>49.11212062816623</v>
+        <v>49.75261032471531</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>20.77426728321672</v>
+        <v>18.18886750136023</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.4194081595047057</v>
+        <v>0.3900613075357082</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>0.0148271300024765</v>
+        <v>-0.1395235368133979</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>6770</v>
+        <v>6698</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>旭暉應材</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>330.4379552375836</v>
+        <v>391.6816951447289</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>71.09999999999999</v>
+        <v>40.05</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>46.51360183865524</v>
+        <v>47.9846038159286</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>17.16066617818829</v>
+        <v>29.21031095155858</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.6783914785034496</v>
+        <v>0.2556492825080236</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-1.255069642368554</v>
+        <v>-0.6451901146337116</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>6658</v>
+        <v>6531</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>聯策</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>306.2810580083481</v>
+        <v>383.7554484383441</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>179.5</v>
+        <v>922</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,16 +4845,16 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>42.72182022624174</v>
+        <v>44.93989250651241</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>23.74112169738468</v>
+        <v>19.70161541490256</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.9127745972555924</v>
+        <v>0.6913528299949102</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-4.125172185823336</v>
+        <v>-13.47024695107131</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>6515</v>
+        <v>6725</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>矽科宏晟</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>301.1627714219665</v>
+        <v>383.5367904348528</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>7765</v>
+        <v>305.5</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>40.32504193134784</v>
+        <v>43.21693973076976</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>15.73228466602259</v>
+        <v>21.50047520525937</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.7537787896570529</v>
+        <v>0.1970419132930303</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-129.3450513119197</v>
+        <v>-3.411320418058653</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>6792</v>
+        <v>6561</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>詠業</t>
+          <t>是方</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>300.7196771235001</v>
+        <v>381.3219879093637</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>61.7</v>
+        <v>330.5</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,16 +4951,16 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>41.33368101454595</v>
+        <v>39.09196338881269</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>19.98650759353621</v>
+        <v>20.63001740319667</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.4904762088548507</v>
+        <v>0.3129231034568797</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-0.560243079279067</v>
+        <v>-0.1680527533914375</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>6821</v>
+        <v>6690</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>聯寶</t>
+          <t>安碁資訊</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>294.6709704854222</v>
+        <v>379.4332732063193</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>51.6</v>
+        <v>166.5</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,16 +5004,16 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>33.58037783764908</v>
+        <v>44.63014541075785</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>16.85543691793646</v>
+        <v>14.43662579867491</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.2326609464513606</v>
+        <v>0.3219020244547579</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-1.539659630622465</v>
+        <v>-0.3006336229487034</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>6504</v>
+        <v>6789</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>南六</t>
+          <t>采鈺</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>293.1363339467264</v>
+        <v>378.5211467168094</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>36</v>
+        <v>515</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,16 +5057,16 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>43.4925053262406</v>
+        <v>49.29976006274612</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>14.16677227278365</v>
+        <v>11.45613657085052</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.5408079349634326</v>
+        <v>0.5078244177819691</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>0.1152682033011751</v>
+        <v>-0.7010781471795562</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>6598</v>
+        <v>6597</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>ABC-KY</t>
+          <t>立誠</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>286.170001218299</v>
+        <v>376.4787716480552</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>22.85</v>
+        <v>67.8</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,16 +5110,16 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>40.50646624594779</v>
+        <v>51.52220358926256</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>15.74469755350476</v>
+        <v>14.4416454967116</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.2679943096239905</v>
+        <v>0.2217467632214176</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-0.0488682956032888</v>
+        <v>-2.553841087692786</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, williams_r_recovery</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>6823</v>
+        <v>6515</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>濾能</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>285.8192074796418</v>
+        <v>376.1627714219665</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>66.2</v>
+        <v>7765</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,49 +5163,49 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>38.92273476343238</v>
+        <v>40.32504192944973</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>15.08127757059748</v>
+        <v>15.73228471199892</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.6895683299719043</v>
+        <v>0.7537787896570529</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L89" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M89" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>0.1456141922282876</v>
+        <v>-129.3450513143999</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>6796</v>
+        <v>6715</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>晉弘</t>
+          <t>嘉基</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>284.5319982048787</v>
+        <v>375.7961387345421</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>59.2</v>
+        <v>391.5</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>48.76813216284216</v>
+        <v>41.02153305558943</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>22.06564320097512</v>
+        <v>17.16508098089622</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.9376498127101636</v>
+        <v>2.332115911198549</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.381655109705624</v>
+        <v>-6.670494945067979</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>6606</v>
+        <v>6741</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>建德工業</t>
+          <t>91APP*-KY</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>279.710684780087</v>
+        <v>375.1821582725876</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>25.05</v>
+        <v>60</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,16 +5269,16 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>46.69532408264269</v>
+        <v>40.98150273237917</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>13.03688376972354</v>
+        <v>9.099618418777792</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.5178732407245416</v>
+        <v>1.474235345176557</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.0106047876657327</v>
+        <v>-0.1252753070053037</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>6720</v>
+        <v>6510</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>久昌</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>278.6817965115297</v>
+        <v>372.8793682236349</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>140.5</v>
+        <v>2855</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,49 +5322,49 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>44.19777687320438</v>
+        <v>37.5037168934422</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>22.10298401443308</v>
+        <v>20.50776648792229</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.3567069208864492</v>
+        <v>0.6169599725795567</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L92" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M92" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>0.6345178227360093</v>
+        <v>-53.90204377594968</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>6570</v>
+        <v>6763</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>維田</t>
+          <t>綠界科技</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>277.1518155960308</v>
+        <v>372.2888543904213</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>52.8</v>
+        <v>45.9</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>49.7526103334078</v>
+        <v>44.24551976832949</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>18.1888675532136</v>
+        <v>14.3906360408211</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.3900613075357082</v>
+        <v>0.7669989018105312</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-0.1395235368133979</v>
+        <v>-0.1506834430244326</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>6531</v>
+        <v>6640</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>均華</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>273.755448438344</v>
+        <v>366.708003289398</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>922</v>
+        <v>995</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,16 +5428,16 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>44.9398925140591</v>
+        <v>38.78904336163709</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>19.70161537019482</v>
+        <v>19.61234233846608</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.6913528299949102</v>
+        <v>0.6161250987838414</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-13.47024695107131</v>
+        <v>2.992810436708212</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>6533</v>
+        <v>6588</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>東典光電</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>271.019284031169</v>
+        <v>365.7707035167654</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>191.5</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>39.3447855008506</v>
+        <v>27.44225560475532</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>9.453825797997183</v>
+        <v>21.34932604040345</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.4116433795171787</v>
+        <v>0.5217914986181071</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>0.06783734483694551</v>
+        <v>-0.6701959009609251</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>6592</v>
+        <v>6667</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>和潤企業</t>
+          <t>信紘科</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>269.0768804752871</v>
+        <v>363.4068678810371</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>59.4</v>
+        <v>255</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>37.27174996187637</v>
+        <v>40.36420614039848</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>26.75495347802769</v>
+        <v>11.25283339005108</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>1.107688047528706</v>
+        <v>0.326947522433445</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-0.4962869640803922</v>
+        <v>-2.09710506603584</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>6789</v>
+        <v>6695</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>采鈺</t>
+          <t>芯鼎</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>268.5211467168094</v>
+        <v>354.5040666521084</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>515</v>
+        <v>53.7</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>49.29976011625968</v>
+        <v>44.25081250665493</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>11.45613658746094</v>
+        <v>20.01410549803342</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.5078244177819691</v>
+        <v>0.2781308503205539</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-0.7010781488968267</v>
+        <v>-1.002137708427648</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>6561</v>
+        <v>6768</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>是方</t>
+          <t>志強-KY</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>266.3219879093637</v>
+        <v>351.2708120455608</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>330.5</v>
+        <v>71.2</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,16 +5640,16 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>39.09196338881269</v>
+        <v>26.43697351487201</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>20.63001740319667</v>
+        <v>28.28702706409566</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.3129231034568797</v>
+        <v>0.5996688685354499</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-0.1680527530098325</v>
+        <v>-1.143813432097494</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>6761</v>
+        <v>6689</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>穩得</t>
+          <t>伊雲谷</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>265.8147523292832</v>
+        <v>344.0970528510371</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>181</v>
+        <v>63.8</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,16 +5693,16 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>42.6093830120512</v>
+        <v>41.37266848906904</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>12.64427597539331</v>
+        <v>15.33572375315994</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.9961010342967304</v>
+        <v>0.3667007007287019</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-0.9036602854693992</v>
+        <v>-0.0371268968194189</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>6670</v>
+        <v>6584</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>復盛應用</t>
+          <t>南俊國際</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>265.641793367272</v>
+        <v>341.5014138720194</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>261.5</v>
+        <v>663</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>47.69069852276025</v>
+        <v>48.49963351571066</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>19.30187582463844</v>
+        <v>13.68941483089875</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.3084556471968471</v>
+        <v>0.250640185268231</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-0.626266794751082</v>
+        <v>-1.546796010479504</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>6498</v>
+        <v>6835</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>久禾光</t>
+          <t>圓裕</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>261.1769073280221</v>
+        <v>329.5204088787291</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>91.8</v>
+        <v>34.35</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,16 +5799,16 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>41.48827068366163</v>
+        <v>34.32925264841154</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>18.97596250747008</v>
+        <v>25.77345051491323</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.3255869692953529</v>
+        <v>0.7828998352280849</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-0.9173587368704204</v>
+        <v>-0.044540859631272</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>6741</v>
+        <v>6838</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>91APP*-KY</t>
+          <t>台新藥</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>260.1821582725876</v>
+        <v>327.6792416585641</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>60</v>
+        <v>24.3</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,16 +5852,16 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>40.98150287444773</v>
+        <v>45.03139661293757</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>9.099618355048433</v>
+        <v>12.74871241653329</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>1.474235345176557</v>
+        <v>0.674281140920425</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.1252753069862333</v>
+        <v>0.1029520869291077</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>6763</v>
+        <v>6550</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>綠界科技</t>
+          <t>北極星藥業-KY</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>257.2888543904212</v>
+        <v>321.8925943145946</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>45.9</v>
+        <v>13</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>44.24551987226324</v>
+        <v>41.30874512907399</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>14.39063609050188</v>
+        <v>20.49689756833377</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.7669989018105312</v>
+        <v>0.8866924089041965</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-0.150683442986275</v>
+        <v>0.1399382495785264</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>6605</v>
+        <v>6657</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>帝寶</t>
+          <t>華安</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>255.499487966438</v>
+        <v>316.3577815541773</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>126</v>
+        <v>35.3</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,16 +5958,16 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>33.57567602890413</v>
+        <v>43.26029121542877</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>13.53493560536608</v>
+        <v>17.09276671580403</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>2.449948796643803</v>
+        <v>0.5226253375601738</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-1.289102729120522</v>
+        <v>0.1999607572648161</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>6512</v>
+        <v>6770</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>啟發電</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>254.6604456895</v>
+        <v>315.6648838856335</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>20.25</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>52.23819969018646</v>
+        <v>46.51360184470683</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>8.434207485140645</v>
+        <v>17.16066618852149</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.441555801832234</v>
+        <v>0.7094367060605318</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>0.3200060053442046</v>
+        <v>-1.255069642435334</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>6643</v>
+        <v>6792</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>M31</t>
+          <t>詠業</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>246.7443182003722</v>
+        <v>300.7196771235001</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>442</v>
+        <v>61.7</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>35.73910301332627</v>
+        <v>41.3336809798276</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>18.7914595652746</v>
+        <v>19.98650754712201</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>1.104121604883709</v>
+        <v>0.4904762088548507</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-0.1686557521434259</v>
+        <v>-0.5602430792981412</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>6803</v>
+        <v>6821</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>崑鼎</t>
+          <t>聯寶</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>239.9642073391052</v>
+        <v>294.6709704854222</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>274</v>
+        <v>51.6</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,16 +6117,16 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>28.53793051756372</v>
+        <v>33.58037781821987</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>36.65968897583714</v>
+        <v>16.85543697347252</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.2369421464651919</v>
+        <v>0.2326609464513606</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-1.579237518457104</v>
+        <v>-1.53965963085142</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>6690</v>
+        <v>6823</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>安碁資訊</t>
+          <t>濾能</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>239.4332732063192</v>
+        <v>285.8192074796418</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>166.5</v>
+        <v>66.2</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,16 +6170,16 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>44.63014542089192</v>
+        <v>38.92273470789025</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>14.43662579384633</v>
+        <v>15.08127757059748</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.3219020244547579</v>
+        <v>0.6895683299719043</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.3006336228533155</v>
+        <v>0.1456141922569021</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>6532</v>
+        <v>6671</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>瑞耘</t>
+          <t>三能-KY</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>237.9545737167573</v>
+        <v>285.4396243587977</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>78</v>
+        <v>24.6</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,16 +6223,16 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>31.24913596176788</v>
+        <v>33.09146773114014</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>16.15453997305537</v>
+        <v>29.50746934964003</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.7762651967701159</v>
+        <v>0.0497590392409964</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-0.9832574007868208</v>
+        <v>0.1081590525231321</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>6546</v>
+        <v>6720</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>正基</t>
+          <t>久昌</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>223.4927247787704</v>
+        <v>278.6817965115297</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>67.59999999999999</v>
+        <v>140.5</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,16 +6276,16 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>40.83189043323112</v>
+        <v>44.19777687320438</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>13.29868805191212</v>
+        <v>22.1029839707829</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.752247196514949</v>
+        <v>0.3567069208864492</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-0.3719280813374186</v>
+        <v>0.6345178230222275</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>6768</v>
+        <v>6533</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>志強-KY</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>216.2708120455608</v>
+        <v>271.019284031169</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>71.2</v>
+        <v>191.5</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>26.43697348901966</v>
+        <v>39.34478541705536</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>28.2870270438844</v>
+        <v>9.453825813729642</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.5996688685354499</v>
+        <v>0.4116433795171787</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-1.14381343142971</v>
+        <v>0.06783734416913841</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>6680</v>
+        <v>6761</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>鑫創電子</t>
+          <t>穩得</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>215.1806078656739</v>
+        <v>265.8147523292832</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>49.35</v>
+        <v>181</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>50.04762780743115</v>
+        <v>42.60938299468615</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>3.979599990881895</v>
+        <v>12.64427604056821</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.0916956364419161</v>
+        <v>0.9961010342967304</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>0.09302350343906959</v>
+        <v>-0.9036602854693992</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>6835</v>
+        <v>6498</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>圓裕</t>
+          <t>久禾光</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>214.5204088787291</v>
+        <v>261.1769073280221</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>34.35</v>
+        <v>91.8</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,16 +6435,16 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>34.32925270989293</v>
+        <v>41.4882705419237</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>25.77345061810469</v>
+        <v>18.97596249194498</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.7828998352280849</v>
+        <v>0.3255869692953529</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.0445408594690934</v>
+        <v>-0.9173587365460693</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>6706</v>
+        <v>6605</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>惠特</t>
+          <t>帝寶</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>211.5132591317279</v>
+        <v>255.499487966438</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,16 +6488,16 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>37.54028330683413</v>
+        <v>33.57567588141866</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>16.35562293039006</v>
+        <v>13.53493576345398</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.2773792467241036</v>
+        <v>2.449948796643803</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-1.519361429098996</v>
+        <v>-1.289102728643541</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>6550</v>
+        <v>6643</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>北極星藥業-KY</t>
+          <t>M31</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>206.8925943145946</v>
+        <v>246.7443182003722</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>13</v>
+        <v>442</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,13 +6541,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>41.30874515337634</v>
+        <v>35.73910293436239</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>20.49689766060369</v>
+        <v>18.79145957529873</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.8866924089041965</v>
+        <v>1.104121604883709</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>0</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>0.1399382496071446</v>
+        <v>-0.1686557511894655</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>6597</v>
+        <v>6692</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>立誠</t>
+          <t>進能服</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>206.4787716480553</v>
+        <v>246.6309442467248</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>67.8</v>
+        <v>25</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,16 +6594,16 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>51.52220359861456</v>
+        <v>41.72174719942128</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>14.44164553937698</v>
+        <v>12.54193452547294</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.2217467632214176</v>
+        <v>0.2419352251399605</v>
       </c>
       <c r="K116" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L116" s="2" t="n">
         <v>0</v>
@@ -6612,31 +6612,31 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-2.553841087597386</v>
+        <v>0.0209835230382586</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, williams_r_recovery</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>6591</v>
+        <v>6803</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>動力-KY</t>
+          <t>崑鼎</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>201.8795914127689</v>
+        <v>239.9642073391053</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>49.4</v>
+        <v>274</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,16 +6647,16 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>31.54900846982505</v>
+        <v>28.53793049864439</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>22.90409399859548</v>
+        <v>36.65968903144845</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>1.305711264294257</v>
+        <v>0.2369421464651919</v>
       </c>
       <c r="K117" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L117" s="2" t="n">
         <v>0</v>
@@ -6665,7 +6665,7 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>-0.4216307769851048</v>
+        <v>-1.579237518361683</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
@@ -6675,21 +6675,21 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>6689</v>
+        <v>6532</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>伊雲谷</t>
+          <t>瑞耘</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>184.0970528510371</v>
+        <v>237.9545737167573</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>63.8</v>
+        <v>78</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,16 +6700,16 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>41.37266849370007</v>
+        <v>31.24913595285118</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>15.33572375105693</v>
+        <v>16.1545400091649</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.3667007007287019</v>
+        <v>0.7762651967701159</v>
       </c>
       <c r="K118" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L118" s="2" t="n">
         <v>0</v>
@@ -6718,31 +6718,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>-0.0371268966286248</v>
+        <v>-0.9832574008631489</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>6754</v>
+        <v>6807</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>匯僑設計</t>
+          <t>峰源-KY</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>179.8881303456991</v>
+        <v>224.0150085429477</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>41.5</v>
+        <v>33.35</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,13 +6753,13 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>31.97657399723987</v>
+        <v>46.52416976153248</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>18.93448359888314</v>
+        <v>13.95221314332964</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.5416796400835713</v>
+        <v>0.333634743756815</v>
       </c>
       <c r="K119" s="2" t="n">
         <v>0</v>
@@ -6771,31 +6771,31 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>-0.398411469049779</v>
+        <v>0.07533203571149159</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>6657</v>
+        <v>6546</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>華安</t>
+          <t>正基</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>176.3577815541773</v>
+        <v>223.4927247787704</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>35.3</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,16 +6806,16 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>43.26029149550806</v>
+        <v>40.83189033534597</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>17.09276660438259</v>
+        <v>13.29868819812367</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.5226253375601738</v>
+        <v>0.752247196514949</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L120" s="2" t="n">
         <v>0</v>
@@ -6824,31 +6824,31 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>0.1999607567496704</v>
+        <v>-0.3719280812801768</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>6671</v>
+        <v>6558</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>三能-KY</t>
+          <t>興能高</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>170.4396243587977</v>
+        <v>218.1066860659051</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>24.6</v>
+        <v>29.8</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,16 +6859,16 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>33.09146775288033</v>
+        <v>46.94589364220873</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>29.50746914974185</v>
+        <v>16.41761503232766</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.0497590392409964</v>
+        <v>0.4195210839764871</v>
       </c>
       <c r="K121" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L121" s="2" t="n">
         <v>0</v>
@@ -6877,31 +6877,31 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>0.1081590525422119</v>
+        <v>0.0660881360678495</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>6552</v>
+        <v>6674</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>易華電</t>
+          <t>鋐寶科技</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>150.7910911011637</v>
+        <v>217.3706975194452</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>29.45</v>
+        <v>16.8</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,13 +6912,13 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>45.23529017422943</v>
+        <v>40.38139183846709</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>11.04092159257618</v>
+        <v>18.13934322261268</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.6252321844502756</v>
+        <v>0.4983078002169389</v>
       </c>
       <c r="K122" s="2" t="n">
         <v>0</v>
@@ -6930,31 +6930,31 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>-0.08376396773371179</v>
+        <v>-0.0226857405212607</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>6692</v>
+        <v>6680</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>進能服</t>
+          <t>鑫創電子</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>131.6309442467248</v>
+        <v>215.1806078656739</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>25</v>
+        <v>49.35</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6965,13 +6965,13 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>41.721747022876</v>
+        <v>50.04762709247905</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>12.54193451093085</v>
+        <v>3.979599990881894</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.2419352251399605</v>
+        <v>0.0916956364419161</v>
       </c>
       <c r="K123" s="2" t="n">
         <v>0</v>
@@ -6983,31 +6983,31 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>0.0209835230954973</v>
+        <v>0.0930235033627497</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>6807</v>
+        <v>6706</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>峰源-KY</t>
+          <t>惠特</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>84.01500854294758</v>
+        <v>211.513259131728</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>33.35</v>
+        <v>139</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7018,13 +7018,13 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>46.52416899355051</v>
+        <v>37.54028330554185</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>13.95221324520809</v>
+        <v>16.35562291396795</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.333634743756815</v>
+        <v>0.2773792467241036</v>
       </c>
       <c r="K124" s="2" t="n">
         <v>0</v>
@@ -7036,31 +7036,31 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>0.0753320359022841</v>
+        <v>-1.519361429137161</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>6558</v>
+        <v>6591</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>興能高</t>
+          <t>動力-KY</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v/>
       </c>
       <c r="D125" s="2" t="n">
-        <v>78.106686065905</v>
+        <v>201.8795914127692</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>29.8</v>
+        <v>49.4</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
@@ -7071,13 +7071,13 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>46.9458938339604</v>
+        <v>31.54900827599663</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>16.41761494540039</v>
+        <v>22.90409423219014</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>0.4195210839764871</v>
+        <v>1.305711264294257</v>
       </c>
       <c r="K125" s="2" t="n">
         <v>0</v>
@@ -7089,31 +7089,31 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>0.06608813593429599</v>
+        <v>-0.4216307764317983</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>6838</v>
+        <v>6754</v>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>台新藥</t>
+          <t>匯僑設計</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
         <v/>
       </c>
       <c r="D126" s="2" t="n">
-        <v>77.67924165856277</v>
+        <v>179.8881303456991</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>24.3</v>
+        <v>41.5</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -7124,13 +7124,13 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>45.03139655084569</v>
+        <v>31.97657396369875</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>12.74871239995593</v>
+        <v>18.93448359424568</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>0.674281140920425</v>
+        <v>0.5416796400835713</v>
       </c>
       <c r="K126" s="2" t="n">
         <v>0</v>
@@ -7142,31 +7142,31 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>0.1029520869004869</v>
+        <v>-0.398411468954379</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>6674</v>
+        <v>6552</v>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>鋐寶科技</t>
+          <t>易華電</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
         <v/>
       </c>
       <c r="D127" s="2" t="n">
-        <v>77.37069751944527</v>
+        <v>150.7910911011637</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>16.8</v>
+        <v>29.45</v>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
@@ -7177,16 +7177,16 @@
         <v>0</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>40.38139187665453</v>
+        <v>45.23529014758144</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>18.13934308357284</v>
+        <v>11.04092161165751</v>
       </c>
       <c r="J127" s="2" t="n">
-        <v>0.4983078002169389</v>
+        <v>0.6252321844502756</v>
       </c>
       <c r="K127" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L127" s="2" t="n">
         <v>0</v>
@@ -7195,11 +7195,11 @@
         <v>-1</v>
       </c>
       <c r="N127" s="2" t="n">
-        <v>-0.0226857404831003</v>
+        <v>-0.08376396779094911</v>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>

--- a/output/full_scan/batch_seq7_2026-07-09.xlsx
+++ b/output/full_scan/batch_seq7_2026-07-09.xlsx
@@ -898,21 +898,21 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>6579</v>
+        <v>6782</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>研揚</t>
+          <t>視陽</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>830.0519318813801</v>
+        <v>816.4694015700398</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>168</v>
+        <v>208</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,16 +923,16 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>55.65079568800395</v>
+        <v>61.2161079898446</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>22.69065329718225</v>
+        <v>18.98883101348961</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.92462148803372</v>
+        <v>1.738489463039223</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.7628516712453965</v>
+        <v>1.851998813488339</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6782</v>
+        <v>6790</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>視陽</t>
+          <t>永豐實</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>816.4694015700398</v>
+        <v>797.5848642475654</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>208</v>
+        <v>40.6</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,16 +976,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>61.2161079898446</v>
+        <v>56.06017041130701</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>18.98883101348961</v>
+        <v>27.42534162084732</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1.738489463039223</v>
+        <v>2.216894408836775</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>1.851998813488339</v>
+        <v>0.0200650518973029</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6672</v>
+        <v>6579</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>騰輝電子-KY</t>
+          <t>研揚</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>813.9820381707417</v>
+        <v>790.0519318813801</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>298</v>
+        <v>168</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,13 +1029,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>63.28453907555873</v>
+        <v>55.65079568800395</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>44.90669516572874</v>
+        <v>22.69065329718225</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.4074601068240206</v>
+        <v>0.92462148803372</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>0</v>
@@ -1047,7 +1047,7 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.909622065573938</v>
+        <v>0.7628516712453965</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -1057,21 +1057,21 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6790</v>
+        <v>6672</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>永豐實</t>
+          <t>騰輝電子-KY</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>797.5848642475654</v>
+        <v>773.9820381707417</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>40.6</v>
+        <v>298</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,13 +1082,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>56.06017041130701</v>
+        <v>63.28453907555873</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>27.42534162084732</v>
+        <v>44.90669516572874</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>2.216894408836775</v>
+        <v>0.4074601068240206</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>0</v>
@@ -1100,11 +1100,11 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0.0200650518973029</v>
+        <v>0.909622065573938</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>785.1053716558544</v>
+        <v>745.1053716558544</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>199.5</v>
@@ -1852,21 +1852,21 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6526</v>
+        <v>6494</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>達發</t>
+          <t>九齊</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>620.8358868881099</v>
+        <v>605.6281069906465</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>652</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,49 +1877,49 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>46.55920794044477</v>
+        <v>54.75708981889597</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>12.50977640156015</v>
+        <v>30.79711053846729</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.3180578006867144</v>
+        <v>0.4960974403011379</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="M27" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>-3.836454092270575</v>
+        <v>-0.4436447065226803</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6494</v>
+        <v>6548</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>九齊</t>
+          <t>長科*</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>605.6281069906465</v>
+        <v>605.0684096141974</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,49 +1930,49 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>54.75708981889597</v>
+        <v>49.32164392833502</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>30.79711053846729</v>
+        <v>35.19220546615367</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.4960974403011379</v>
+        <v>0.4280797026316167</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M28" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>-0.4436447065226803</v>
+        <v>-1.606830051550298</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, invest_trust_buy_2d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6548</v>
+        <v>6776</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>長科*</t>
+          <t>展碁國際</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>605.0684096141974</v>
+        <v>602.1172151615042</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>82.90000000000001</v>
+        <v>55.7</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,49 +1983,49 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>49.32164392833502</v>
+        <v>44.07719400615863</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>35.19220546615367</v>
+        <v>15.16728503789413</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.4280797026316167</v>
+        <v>0.4556270969896387</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M29" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>-1.606830051550298</v>
+        <v>0.007830528605297499</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, invest_trust_buy_2d, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6776</v>
+        <v>6719</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>展碁國際</t>
+          <t>力智</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>602.1172151615042</v>
+        <v>600.4071475628472</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>55.7</v>
+        <v>266.5</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>44.07719400615863</v>
+        <v>50.77748288044828</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>15.16728503789413</v>
+        <v>36.36714290865228</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.4556270969896387</v>
+        <v>0.4679120686323972</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.007830528605297499</v>
+        <v>-2.178105202121177</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, stronger_than_market, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6719</v>
+        <v>6534</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>力智</t>
+          <t>正瀚-創</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>600.4071475628472</v>
+        <v>596.5304830346231</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>266.5</v>
+        <v>93</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>50.77748288044828</v>
+        <v>56.377685820084</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>36.36714290865228</v>
+        <v>15.95026664477515</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.4679120686323972</v>
+        <v>1.365323079628226</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>-2.178105202121177</v>
+        <v>0.3359677804920924</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6534</v>
+        <v>6651</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>正瀚-創</t>
+          <t>全宇昕</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>596.5304830346231</v>
+        <v>596.327139434096</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>93</v>
+        <v>153</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>56.377685820084</v>
+        <v>52.85462862539603</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>15.95026664477515</v>
+        <v>29.15820876787029</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>1.365323079628226</v>
+        <v>0.5657071327213851</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.3359677804920924</v>
+        <v>-0.3302301955753322</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6651</v>
+        <v>6693</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>全宇昕</t>
+          <t>廣閎科</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>596.327139434096</v>
+        <v>592.7668022939393</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>153</v>
+        <v>236.5</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,13 +2195,13 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>52.85462862539603</v>
+        <v>57.38882725730897</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>29.15820876787029</v>
+        <v>48.35219013904855</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.5657071327213851</v>
+        <v>0.7093456386997857</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>-0.3302301955753322</v>
+        <v>-0.8913554387701943</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6693</v>
+        <v>6829</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>廣閎科</t>
+          <t>千附精密</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>592.7668022939393</v>
+        <v>582.0746388788924</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>236.5</v>
+        <v>222</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,16 +2248,16 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>57.38882725730897</v>
+        <v>53.37132264412852</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>48.35219013904855</v>
+        <v>12.80794466052242</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.7093456386997857</v>
+        <v>1.029161936934242</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>-0.8913554387701943</v>
+        <v>0.134213562158755</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6829</v>
+        <v>6526</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>千附精密</t>
+          <t>達發</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>582.0746388788924</v>
+        <v>580.8358868881099</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>222</v>
+        <v>652</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,29 +2301,29 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>53.37132264412852</v>
+        <v>46.55920794044477</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>12.80794466052242</v>
+        <v>12.50977640156015</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>1.029161936934242</v>
+        <v>0.3180578006867144</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L35" s="2" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="M35" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>0.134213562158755</v>
+        <v>-3.836454092270575</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -2753,21 +2753,21 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6641</v>
+        <v>6757</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>基士德-KY</t>
+          <t>台灣虎航-創</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>541.3480499949726</v>
+        <v>539.6201191390852</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>18.55</v>
+        <v>58.2</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>52.15916601029208</v>
+        <v>47.89947150532576</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>21.53463700116355</v>
+        <v>33.4044542250839</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.2348049994972524</v>
+        <v>0.3874529482200982</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.0789543981768993</v>
+        <v>-0.510026576499796</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6757</v>
+        <v>6556</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>台灣虎航-創</t>
+          <t>勝品</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>539.6201191390852</v>
+        <v>537.7912947879956</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>58.2</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>47.89947150532576</v>
+        <v>43.50049532804022</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>33.4044542250839</v>
+        <v>25.4175389739355</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.3874529482200982</v>
+        <v>4.507926746338204</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>-0.510026576499796</v>
+        <v>-0.193538167136914</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6556</v>
+        <v>6613</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>勝品</t>
+          <t>朋億*</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>537.7912947879956</v>
+        <v>532.2781759184518</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>70.59999999999999</v>
+        <v>321</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>43.50049532804022</v>
+        <v>48.1548853306832</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>25.4175389739355</v>
+        <v>26.18091668333613</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>4.507926746338204</v>
+        <v>0.3491639708233205</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-0.193538167136914</v>
+        <v>-8.294732397284093</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6668</v>
+        <v>6486</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>中揚光</t>
+          <t>互動</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>534.0954600328597</v>
+        <v>526.4315539908017</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>37.9</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,16 +2937,16 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>44.24061600837763</v>
+        <v>54.46584108495598</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>17.49634825636789</v>
+        <v>22.52926446869758</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.2315904586944201</v>
+        <v>0.7014900816502103</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-0.5166812948567168</v>
+        <v>0.2434784200002912</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6613</v>
+        <v>6541</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>朋億*</t>
+          <t>泰福-KY</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>532.2781759184518</v>
+        <v>520.788563706419</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>321</v>
+        <v>40.8</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,16 +2990,16 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>48.1548853306832</v>
+        <v>50.37825055393518</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>26.18091668333613</v>
+        <v>15.95431463490334</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.3491639708233205</v>
+        <v>0.4791819830682827</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-8.294732397284093</v>
+        <v>-0.0515945649777843</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6669</v>
+        <v>6684</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>安格</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>527.7527193266883</v>
+        <v>513.5871514814752</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>5040</v>
+        <v>53.9</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,49 +3043,49 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>51.96524510439431</v>
+        <v>48.12188760072574</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>13.16601854784374</v>
+        <v>34.74033046096234</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>1.239935985599949</v>
+        <v>0.2555517275361595</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L49" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M49" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>35.82695697358312</v>
+        <v>-0.844057614690052</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6486</v>
+        <v>6722</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>互動</t>
+          <t>輝創</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>526.4315539908017</v>
+        <v>509.7704691092051</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>83.09999999999999</v>
+        <v>35.45</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>54.46584108495598</v>
+        <v>41.78422157427065</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>22.52926446869758</v>
+        <v>36.62134005229357</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.7014900816502103</v>
+        <v>0.1865728134092482</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>0.2434784200002912</v>
+        <v>0.0319693211539622</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6541</v>
+        <v>6771</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>泰福-KY</t>
+          <t>平和環保-創</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>520.788563706419</v>
+        <v>505.9485006770078</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>40.8</v>
+        <v>39.8</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,16 +3149,16 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>50.37825055393518</v>
+        <v>44.11121485010584</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>15.95431463490334</v>
+        <v>20.97283053484768</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.4791819830682827</v>
+        <v>0.3808665749470042</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-0.0515945649777843</v>
+        <v>0.0462064449937836</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6684</v>
+        <v>6641</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>安格</t>
+          <t>基士德-KY</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>513.5871514814752</v>
+        <v>501.3480499949725</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>53.9</v>
+        <v>18.55</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>48.12188760072574</v>
+        <v>52.15916601029208</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>34.74033046096234</v>
+        <v>21.53463700116355</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.2555517275361595</v>
+        <v>0.2348049994972524</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>-0.844057614690052</v>
+        <v>0.0789543981768993</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6722</v>
+        <v>6756</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>輝創</t>
+          <t>威鋒電子</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>509.7704691092051</v>
+        <v>498.5706487819775</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>35.45</v>
+        <v>99.7</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>41.78422157427065</v>
+        <v>51.11622393290391</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>36.62134005229357</v>
+        <v>18.43002931375125</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.1865728134092482</v>
+        <v>0.719580924508797</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.0319693211539622</v>
+        <v>-0.0941166256695159</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, stronger_than_market</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6771</v>
+        <v>6805</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>平和環保-創</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>505.9485006770078</v>
+        <v>498.2261690857841</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>39.8</v>
+        <v>1460</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,16 +3308,16 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>44.11121485010584</v>
+        <v>35.04999473985863</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>20.97283053484768</v>
+        <v>23.31580815943655</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.3808665749470042</v>
+        <v>1.466381395435663</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.0462064449937836</v>
+        <v>-27.45016259752049</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, stronger_than_market</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6756</v>
+        <v>6530</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>威鋒電子</t>
+          <t>創威</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>498.5706487819775</v>
+        <v>496.8663280777081</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>99.7</v>
+        <v>83</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,16 +3361,16 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>51.11622393290391</v>
+        <v>35.42061692529114</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>18.43002931375125</v>
+        <v>22.55340177651775</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.719580924508797</v>
+        <v>0.6051592319693341</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>-0.0941166256695159</v>
+        <v>-0.1612898038329095</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6805</v>
+        <v>6668</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>中揚光</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>498.2261690857841</v>
+        <v>494.0954600328597</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>1460</v>
+        <v>37.9</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>35.04999473985863</v>
+        <v>44.24061600837763</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>23.31580815943655</v>
+        <v>17.49634825636789</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>1.466381395435663</v>
+        <v>0.2315904586944201</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-27.45016259752049</v>
+        <v>-0.5166812948567168</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6530</v>
+        <v>6669</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>創威</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>496.8663280777081</v>
+        <v>487.7527193266883</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>83</v>
+        <v>5040</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,29 +3467,29 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>35.42061692529114</v>
+        <v>51.96524510439431</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>22.55340177651775</v>
+        <v>13.16601854784374</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.6051592319693341</v>
+        <v>1.239935985599949</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L57" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M57" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-0.1612898038329095</v>
+        <v>35.82695697358312</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -3548,21 +3548,21 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6581</v>
+        <v>6691</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>鋼聯</t>
+          <t>洋基工程</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>487.4493408512781</v>
+        <v>484.1849016766411</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>106.5</v>
+        <v>708</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>43.64214916955456</v>
+        <v>47.83081928113256</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>11.34799022438651</v>
+        <v>26.21879230494516</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>1.861734772157725</v>
+        <v>0.3184901676641075</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-0.0759752293400259</v>
+        <v>-8.401246741242378</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6691</v>
+        <v>6830</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>洋基工程</t>
+          <t>汎銓</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>484.1849016766411</v>
+        <v>482.9114658730273</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>708</v>
+        <v>416.5</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>47.83081928113256</v>
+        <v>31.57675210294522</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>26.21879230494516</v>
+        <v>25.83060349809814</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.3184901676641075</v>
+        <v>0.8696450274370079</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-8.401246741242378</v>
+        <v>-4.110552602012078</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6830</v>
+        <v>6788</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>汎銓</t>
+          <t>華景電</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>482.9114658730273</v>
+        <v>481.9701892520345</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>416.5</v>
+        <v>403.5</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,49 +3679,49 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>31.57675210294522</v>
+        <v>42.06927033991832</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>25.83060349809814</v>
+        <v>8.618651842756288</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.8696450274370079</v>
+        <v>0.4669477995439862</v>
       </c>
       <c r="K61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="L61" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M61" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-4.110552602012078</v>
+        <v>-3.771028098114664</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6788</v>
+        <v>6614</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>資拓宏宇</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>481.9701892520345</v>
+        <v>472.1724104726767</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>403.5</v>
+        <v>40</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,49 +3732,49 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>42.06927033991832</v>
+        <v>49.11212072275216</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>8.618651842756288</v>
+        <v>20.77426729531906</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.4669477995439862</v>
+        <v>0.4194081595047057</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L62" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M62" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-3.771028098114664</v>
+        <v>0.0148271299643166</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, invest_trust_buy_2d, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6614</v>
+        <v>6581</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>資拓宏宇</t>
+          <t>鋼聯</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>472.1724104726767</v>
+        <v>467.4493408512781</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>40</v>
+        <v>106.5</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>49.11212072275216</v>
+        <v>43.64214916955456</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>20.77426729531906</v>
+        <v>11.34799022438651</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.4194081595047057</v>
+        <v>1.861734772157725</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>1</v>
@@ -3803,11 +3803,11 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.0148271299643166</v>
+        <v>-0.0759752293400259</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
@@ -4820,21 +4820,21 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>6531</v>
+        <v>6725</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>矽科宏晟</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>383.7554484383441</v>
+        <v>383.5367904348528</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>922</v>
+        <v>305.5</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,16 +4845,16 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>44.93989250651241</v>
+        <v>43.21693973076976</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>19.70161541490256</v>
+        <v>21.50047520525937</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.6913528299949102</v>
+        <v>0.1970419132930303</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-13.47024695107131</v>
+        <v>-3.411320418058653</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>6725</v>
+        <v>6561</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>矽科宏晟</t>
+          <t>是方</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>383.5367904348528</v>
+        <v>381.3219879093637</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>305.5</v>
+        <v>330.5</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,16 +4898,16 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>43.21693973076976</v>
+        <v>39.09196338881269</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>21.50047520525937</v>
+        <v>20.63001740319667</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.1970419132930303</v>
+        <v>0.3129231034568797</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-3.411320418058653</v>
+        <v>-0.1680527533914375</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>6561</v>
+        <v>6690</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>是方</t>
+          <t>安碁資訊</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>381.3219879093637</v>
+        <v>379.4332732063193</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>330.5</v>
+        <v>166.5</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,16 +4951,16 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>39.09196338881269</v>
+        <v>44.63014541075785</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>20.63001740319667</v>
+        <v>14.43662579867491</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.3129231034568797</v>
+        <v>0.3219020244547579</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-0.1680527533914375</v>
+        <v>-0.3006336229487034</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>6690</v>
+        <v>6789</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>安碁資訊</t>
+          <t>采鈺</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>379.4332732063193</v>
+        <v>378.5211467168094</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>166.5</v>
+        <v>515</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>44.63014541075785</v>
+        <v>49.29976006274612</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>14.43662579867491</v>
+        <v>11.45613657085052</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.3219020244547579</v>
+        <v>0.5078244177819691</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>4</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-0.3006336229487034</v>
+        <v>-0.7010781471795562</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>6789</v>
+        <v>6597</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>采鈺</t>
+          <t>立誠</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>378.5211467168094</v>
+        <v>376.4787716480552</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>515</v>
+        <v>67.8</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,16 +5057,16 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>49.29976006274612</v>
+        <v>51.52220358926256</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>11.45613657085052</v>
+        <v>14.4416454967116</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.5078244177819691</v>
+        <v>0.2217467632214176</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-0.7010781471795562</v>
+        <v>-2.553841087692786</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, williams_r_recovery</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>6597</v>
+        <v>6715</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>立誠</t>
+          <t>嘉基</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>376.4787716480552</v>
+        <v>375.7961387345421</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>67.8</v>
+        <v>391.5</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,16 +5110,16 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>51.52220358926256</v>
+        <v>41.02153305558943</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>14.4416454967116</v>
+        <v>17.16508098089622</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.2217467632214176</v>
+        <v>2.332115911198549</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-2.553841087692786</v>
+        <v>-6.670494945067979</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, williams_r_recovery</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>6515</v>
+        <v>6741</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>91APP*-KY</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>376.1627714219665</v>
+        <v>375.1821582725876</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>7765</v>
+        <v>60</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,49 +5163,49 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>40.32504192944973</v>
+        <v>40.98150273237917</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>15.73228471199892</v>
+        <v>9.099618418777792</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.7537787896570529</v>
+        <v>1.474235345176557</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L89" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M89" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-129.3450513143999</v>
+        <v>-0.1252753070053037</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, dealer_buy_3d</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>6715</v>
+        <v>6510</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>嘉基</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>375.7961387345421</v>
+        <v>372.8793682236349</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>391.5</v>
+        <v>2855</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,49 +5216,49 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>41.02153305558943</v>
+        <v>37.5037168934422</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>17.16508098089622</v>
+        <v>20.50776648792229</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>2.332115911198549</v>
+        <v>0.6169599725795567</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L90" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M90" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-6.670494945067979</v>
+        <v>-53.90204377594968</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>6741</v>
+        <v>6763</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>91APP*-KY</t>
+          <t>綠界科技</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>375.1821582725876</v>
+        <v>372.2888543904213</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>60</v>
+        <v>45.9</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,16 +5269,16 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>40.98150273237917</v>
+        <v>44.24551976832949</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>9.099618418777792</v>
+        <v>14.3906360408211</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>1.474235345176557</v>
+        <v>0.7669989018105312</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-0.1252753070053037</v>
+        <v>-0.1506834430244326</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>6510</v>
+        <v>6640</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>均華</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>372.8793682236349</v>
+        <v>366.708003289398</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>2855</v>
+        <v>995</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,49 +5322,49 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>37.5037168934422</v>
+        <v>38.78904336163709</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>20.50776648792229</v>
+        <v>19.61234233846608</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.6169599725795567</v>
+        <v>0.6161250987838414</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L92" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M92" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-53.90204377594968</v>
+        <v>2.992810436708212</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>6763</v>
+        <v>6588</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>綠界科技</t>
+          <t>東典光電</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>372.2888543904213</v>
+        <v>365.7707035167654</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>45.9</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>44.24551976832949</v>
+        <v>27.44225560475532</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>14.3906360408211</v>
+        <v>21.34932604040345</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.7669989018105312</v>
+        <v>0.5217914986181071</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-0.1506834430244326</v>
+        <v>-0.6701959009609251</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>6640</v>
+        <v>6667</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>均華</t>
+          <t>信紘科</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>366.708003289398</v>
+        <v>363.4068678810371</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>995</v>
+        <v>255</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,16 +5428,16 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>38.78904336163709</v>
+        <v>40.36420614039848</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>19.61234233846608</v>
+        <v>11.25283339005108</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.6161250987838414</v>
+        <v>0.326947522433445</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>2.992810436708212</v>
+        <v>-2.09710506603584</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>6588</v>
+        <v>6695</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>東典光電</t>
+          <t>芯鼎</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>365.7707035167654</v>
+        <v>354.5040666521084</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>78.90000000000001</v>
+        <v>53.7</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>27.44225560475532</v>
+        <v>44.25081250665493</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>21.34932604040345</v>
+        <v>20.01410549803342</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.5217914986181071</v>
+        <v>0.2781308503205539</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-0.6701959009609251</v>
+        <v>-1.002137708427648</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>6667</v>
+        <v>6768</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>信紘科</t>
+          <t>志強-KY</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>363.4068678810371</v>
+        <v>351.2708120455608</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>255</v>
+        <v>71.2</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,16 +5534,16 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>40.36420614039848</v>
+        <v>26.43697351487201</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>11.25283339005108</v>
+        <v>28.28702706409566</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.326947522433445</v>
+        <v>0.5996688685354499</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-2.09710506603584</v>
+        <v>-1.143813432097494</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>6695</v>
+        <v>6689</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>芯鼎</t>
+          <t>伊雲谷</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>354.5040666521084</v>
+        <v>344.0970528510371</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>53.7</v>
+        <v>63.8</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,16 +5587,16 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>44.25081250665493</v>
+        <v>41.37266848906904</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>20.01410549803342</v>
+        <v>15.33572375315994</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.2781308503205539</v>
+        <v>0.3667007007287019</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-1.002137708427648</v>
+        <v>-0.0371268968194189</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>6768</v>
+        <v>6531</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>志強-KY</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>351.2708120455608</v>
+        <v>343.755448438344</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>71.2</v>
+        <v>922</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,16 +5640,16 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>26.43697351487201</v>
+        <v>44.93989250651241</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>28.28702706409566</v>
+        <v>19.70161541490256</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.5996688685354499</v>
+        <v>0.6913528299949102</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-1.143813432097494</v>
+        <v>-13.47024695107131</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>6689</v>
+        <v>6584</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>伊雲谷</t>
+          <t>南俊國際</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>344.0970528510371</v>
+        <v>341.5014138720194</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>63.8</v>
+        <v>663</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,16 +5693,16 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>41.37266848906904</v>
+        <v>48.49963351571066</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>15.33572375315994</v>
+        <v>13.68941483089875</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.3667007007287019</v>
+        <v>0.250640185268231</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-0.0371268968194189</v>
+        <v>-1.546796010479504</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>6584</v>
+        <v>6515</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>南俊國際</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>341.5014138720194</v>
+        <v>336.1627714219665</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>663</v>
+        <v>7765</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,29 +5746,29 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>48.49963351571066</v>
+        <v>40.32504192944973</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>13.68941483089875</v>
+        <v>15.73228471199892</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.250640185268231</v>
+        <v>0.7537787896570529</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L100" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M100" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-1.546796010479504</v>
+        <v>-129.3450513143999</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, dealer_buy_3d</t>
         </is>
       </c>
     </row>
@@ -6304,21 +6304,21 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>6533</v>
+        <v>6761</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>穩得</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>271.019284031169</v>
+        <v>265.8147523292832</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>191.5</v>
+        <v>181</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>39.34478541705536</v>
+        <v>42.60938299468615</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>9.453825813729642</v>
+        <v>12.64427604056821</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.4116433795171787</v>
+        <v>0.9961010342967304</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>0.06783734416913841</v>
+        <v>-0.9036602854693992</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>6761</v>
+        <v>6498</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>穩得</t>
+          <t>久禾光</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>265.8147523292832</v>
+        <v>261.1769073280221</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>181</v>
+        <v>91.8</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,16 +6382,16 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>42.60938299468615</v>
+        <v>41.4882705419237</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>12.64427604056821</v>
+        <v>18.97596249194498</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.9961010342967304</v>
+        <v>0.3255869692953529</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-0.9036602854693992</v>
+        <v>-0.9173587365460693</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>6498</v>
+        <v>6605</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>久禾光</t>
+          <t>帝寶</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>261.1769073280221</v>
+        <v>255.499487966438</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>91.8</v>
+        <v>126</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>41.4882705419237</v>
+        <v>33.57567588141866</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>18.97596249194498</v>
+        <v>13.53493576345398</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.3255869692953529</v>
+        <v>2.449948796643803</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>1</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.9173587365460693</v>
+        <v>-1.289102728643541</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>6605</v>
+        <v>6533</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>帝寶</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>255.499487966438</v>
+        <v>251.019284031169</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>126</v>
+        <v>191.5</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,16 +6488,16 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>33.57567588141866</v>
+        <v>39.34478541705536</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>13.53493576345398</v>
+        <v>9.453825813729642</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>2.449948796643803</v>
+        <v>0.4116433795171787</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-1.289102728643541</v>
+        <v>0.06783734416913841</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>6643</v>
+        <v>6558</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>M31</t>
+          <t>興能高</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>246.7443182003722</v>
+        <v>248.1066860659051</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>442</v>
+        <v>29.8</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,16 +6541,16 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>35.73910293436239</v>
+        <v>46.94589364220873</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>18.79145957529873</v>
+        <v>16.41761503232766</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>1.104121604883709</v>
+        <v>0.4195210839764871</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L115" s="2" t="n">
         <v>0</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-0.1686557511894655</v>
+        <v>0.0660881360678495</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>6692</v>
+        <v>6674</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>進能服</t>
+          <t>鋐寶科技</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>246.6309442467248</v>
+        <v>247.3706975194452</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>25</v>
+        <v>16.8</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,13 +6594,13 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>41.72174719942128</v>
+        <v>40.38139183846709</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>12.54193452547294</v>
+        <v>18.13934322261268</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.2419352251399605</v>
+        <v>0.4983078002169389</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>0</v>
@@ -6612,7 +6612,7 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>0.0209835230382586</v>
+        <v>-0.0226857405212607</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
@@ -6622,21 +6622,21 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>6803</v>
+        <v>6643</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>崑鼎</t>
+          <t>M31</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>239.9642073391053</v>
+        <v>246.7443182003722</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>274</v>
+        <v>442</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,16 +6647,16 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>28.53793049864439</v>
+        <v>35.73910293436239</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>36.65968903144845</v>
+        <v>18.79145957529873</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.2369421464651919</v>
+        <v>1.104121604883709</v>
       </c>
       <c r="K117" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L117" s="2" t="n">
         <v>0</v>
@@ -6665,31 +6665,31 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>-1.579237518361683</v>
+        <v>-0.1686557511894655</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>6532</v>
+        <v>6692</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>瑞耘</t>
+          <t>進能服</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>237.9545737167573</v>
+        <v>246.6309442467248</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>78</v>
+        <v>25</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,16 +6700,16 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>31.24913595285118</v>
+        <v>41.72174719942128</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>16.1545400091649</v>
+        <v>12.54193452547294</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.7762651967701159</v>
+        <v>0.2419352251399605</v>
       </c>
       <c r="K118" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L118" s="2" t="n">
         <v>0</v>
@@ -6718,31 +6718,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>-0.9832574008631489</v>
+        <v>0.0209835230382586</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>6807</v>
+        <v>6803</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>峰源-KY</t>
+          <t>崑鼎</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>224.0150085429477</v>
+        <v>239.9642073391053</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>33.35</v>
+        <v>274</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,16 +6753,16 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>46.52416976153248</v>
+        <v>28.53793049864439</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>13.95221314332964</v>
+        <v>36.65968903144845</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.333634743756815</v>
+        <v>0.2369421464651919</v>
       </c>
       <c r="K119" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L119" s="2" t="n">
         <v>0</v>
@@ -6771,31 +6771,31 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>0.07533203571149159</v>
+        <v>-1.579237518361683</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>6546</v>
+        <v>6532</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>正基</t>
+          <t>瑞耘</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>223.4927247787704</v>
+        <v>237.9545737167573</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>67.59999999999999</v>
+        <v>78</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,13 +6806,13 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>40.83189033534597</v>
+        <v>31.24913595285118</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>13.29868819812367</v>
+        <v>16.1545400091649</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.752247196514949</v>
+        <v>0.7762651967701159</v>
       </c>
       <c r="K120" s="2" t="n">
         <v>1</v>
@@ -6824,7 +6824,7 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>-0.3719280812801768</v>
+        <v>-0.9832574008631489</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
@@ -6834,21 +6834,21 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>6558</v>
+        <v>6591</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>興能高</t>
+          <t>動力-KY</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>218.1066860659051</v>
+        <v>231.8795914127692</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>29.8</v>
+        <v>49.4</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,16 +6859,16 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>46.94589364220873</v>
+        <v>31.54900827599663</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>16.41761503232766</v>
+        <v>22.90409423219014</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.4195210839764871</v>
+        <v>1.305711264294257</v>
       </c>
       <c r="K121" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L121" s="2" t="n">
         <v>0</v>
@@ -6877,31 +6877,31 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>0.0660881360678495</v>
+        <v>-0.4216307764317983</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>6674</v>
+        <v>6807</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>鋐寶科技</t>
+          <t>峰源-KY</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>217.3706975194452</v>
+        <v>224.0150085429477</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>16.8</v>
+        <v>33.35</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,13 +6912,13 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>40.38139183846709</v>
+        <v>46.52416976153248</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>18.13934322261268</v>
+        <v>13.95221314332964</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.4983078002169389</v>
+        <v>0.333634743756815</v>
       </c>
       <c r="K122" s="2" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>-0.0226857405212607</v>
+        <v>0.07533203571149159</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
@@ -6940,21 +6940,21 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>6680</v>
+        <v>6546</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>鑫創電子</t>
+          <t>正基</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>215.1806078656739</v>
+        <v>223.4927247787704</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>49.35</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6965,16 +6965,16 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>50.04762709247905</v>
+        <v>40.83189033534597</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>3.979599990881894</v>
+        <v>13.29868819812367</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.0916956364419161</v>
+        <v>0.752247196514949</v>
       </c>
       <c r="K123" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L123" s="2" t="n">
         <v>0</v>
@@ -6983,31 +6983,31 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>0.0930235033627497</v>
+        <v>-0.3719280812801768</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>6706</v>
+        <v>6680</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>惠特</t>
+          <t>鑫創電子</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>211.513259131728</v>
+        <v>215.1806078656739</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>139</v>
+        <v>49.35</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7018,13 +7018,13 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>37.54028330554185</v>
+        <v>50.04762709247905</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>16.35562291396795</v>
+        <v>3.979599990881894</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.2773792467241036</v>
+        <v>0.0916956364419161</v>
       </c>
       <c r="K124" s="2" t="n">
         <v>0</v>
@@ -7036,31 +7036,31 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>-1.519361429137161</v>
+        <v>0.0930235033627497</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>6591</v>
+        <v>6706</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>動力-KY</t>
+          <t>惠特</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v/>
       </c>
       <c r="D125" s="2" t="n">
-        <v>201.8795914127692</v>
+        <v>211.513259131728</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>49.4</v>
+        <v>139</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
@@ -7071,13 +7071,13 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>31.54900827599663</v>
+        <v>37.54028330554185</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>22.90409423219014</v>
+        <v>16.35562291396795</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>1.305711264294257</v>
+        <v>0.2773792467241036</v>
       </c>
       <c r="K125" s="2" t="n">
         <v>0</v>
@@ -7089,31 +7089,31 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>-0.4216307764317983</v>
+        <v>-1.519361429137161</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>6754</v>
+        <v>6552</v>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>匯僑設計</t>
+          <t>易華電</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
         <v/>
       </c>
       <c r="D126" s="2" t="n">
-        <v>179.8881303456991</v>
+        <v>180.7910911011637</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>41.5</v>
+        <v>29.45</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -7124,16 +7124,16 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>31.97657396369875</v>
+        <v>45.23529014758144</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>18.93448359424568</v>
+        <v>11.04092161165751</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>0.5416796400835713</v>
+        <v>0.6252321844502756</v>
       </c>
       <c r="K126" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L126" s="2" t="n">
         <v>0</v>
@@ -7142,31 +7142,31 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>-0.398411468954379</v>
+        <v>-0.08376396779094911</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>6552</v>
+        <v>6754</v>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>易華電</t>
+          <t>匯僑設計</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
         <v/>
       </c>
       <c r="D127" s="2" t="n">
-        <v>150.7910911011637</v>
+        <v>179.8881303456991</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>29.45</v>
+        <v>41.5</v>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
@@ -7177,16 +7177,16 @@
         <v>0</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>45.23529014758144</v>
+        <v>31.97657396369875</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>11.04092161165751</v>
+        <v>18.93448359424568</v>
       </c>
       <c r="J127" s="2" t="n">
-        <v>0.6252321844502756</v>
+        <v>0.5416796400835713</v>
       </c>
       <c r="K127" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L127" s="2" t="n">
         <v>0</v>
@@ -7195,11 +7195,11 @@
         <v>-1</v>
       </c>
       <c r="N127" s="2" t="n">
-        <v>-0.08376396779094911</v>
+        <v>-0.398411468954379</v>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>

--- a/output/full_scan/batch_seq7_2026-07-09.xlsx
+++ b/output/full_scan/batch_seq7_2026-07-09.xlsx
@@ -898,21 +898,21 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>6782</v>
+        <v>6579</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>視陽</t>
+          <t>研揚</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>816.4694015700398</v>
+        <v>830.0519318813801</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>208</v>
+        <v>168</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,16 +923,16 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>61.2161079898446</v>
+        <v>55.65079568800395</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>18.98883101348961</v>
+        <v>22.69065329718225</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1.738489463039223</v>
+        <v>0.92462148803372</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>1.851998813488339</v>
+        <v>0.7628516712453965</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6790</v>
+        <v>6782</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>永豐實</t>
+          <t>視陽</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>797.5848642475654</v>
+        <v>816.4694015700398</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>40.6</v>
+        <v>208</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,16 +976,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>56.06017041130701</v>
+        <v>61.2161079898446</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>27.42534162084732</v>
+        <v>18.98883101348961</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>2.216894408836775</v>
+        <v>1.738489463039223</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.0200650518973029</v>
+        <v>1.851998813488339</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6579</v>
+        <v>6672</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>研揚</t>
+          <t>騰輝電子-KY</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>790.0519318813801</v>
+        <v>813.9820381707417</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>168</v>
+        <v>298</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,13 +1029,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>55.65079568800395</v>
+        <v>63.28453907555873</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>22.69065329718225</v>
+        <v>44.90669516572874</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.92462148803372</v>
+        <v>0.4074601068240206</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>0</v>
@@ -1047,7 +1047,7 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.7628516712453965</v>
+        <v>0.909622065573938</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -1057,21 +1057,21 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6672</v>
+        <v>6790</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>騰輝電子-KY</t>
+          <t>永豐實</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>773.9820381707417</v>
+        <v>797.5848642475654</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>298</v>
+        <v>40.6</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,13 +1082,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>63.28453907555873</v>
+        <v>56.06017041130701</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>44.90669516572874</v>
+        <v>27.42534162084732</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.4074601068240206</v>
+        <v>2.216894408836775</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>0</v>
@@ -1100,11 +1100,11 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0.909622065573938</v>
+        <v>0.0200650518973029</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>745.1053716558544</v>
+        <v>785.1053716558544</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>199.5</v>
@@ -1852,21 +1852,21 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6494</v>
+        <v>6526</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>九齊</t>
+          <t>達發</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>605.6281069906465</v>
+        <v>620.8358868881099</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>652</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,49 +1877,49 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>54.75708981889597</v>
+        <v>46.55920794044477</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>30.79711053846729</v>
+        <v>12.50977640156015</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.4960974403011379</v>
+        <v>0.3180578006867144</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="M27" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>-0.4436447065226803</v>
+        <v>-3.836454092270575</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6548</v>
+        <v>6494</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>長科*</t>
+          <t>九齊</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>605.0684096141974</v>
+        <v>605.6281069906465</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>82.90000000000001</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,49 +1930,49 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>49.32164392833502</v>
+        <v>54.75708981889597</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>35.19220546615367</v>
+        <v>30.79711053846729</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.4280797026316167</v>
+        <v>0.4960974403011379</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M28" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>-1.606830051550298</v>
+        <v>-0.4436447065226803</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, invest_trust_buy_2d, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6776</v>
+        <v>6548</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>展碁國際</t>
+          <t>長科*</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>602.1172151615042</v>
+        <v>605.0684096141974</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>55.7</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,49 +1983,49 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>44.07719400615863</v>
+        <v>49.32164392833502</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>15.16728503789413</v>
+        <v>35.19220546615367</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.4556270969896387</v>
+        <v>0.4280797026316167</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M29" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.007830528605297499</v>
+        <v>-1.606830051550298</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, stronger_than_market, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, invest_trust_buy_2d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6719</v>
+        <v>6776</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>力智</t>
+          <t>展碁國際</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>600.4071475628472</v>
+        <v>602.1172151615042</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>266.5</v>
+        <v>55.7</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>50.77748288044828</v>
+        <v>44.07719400615863</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>36.36714290865228</v>
+        <v>15.16728503789413</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.4679120686323972</v>
+        <v>0.4556270969896387</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>-2.178105202121177</v>
+        <v>0.007830528605297499</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6534</v>
+        <v>6719</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>正瀚-創</t>
+          <t>力智</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>596.5304830346231</v>
+        <v>600.4071475628472</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>93</v>
+        <v>266.5</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>56.377685820084</v>
+        <v>50.77748288044828</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>15.95026664477515</v>
+        <v>36.36714290865228</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>1.365323079628226</v>
+        <v>0.4679120686323972</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.3359677804920924</v>
+        <v>-2.178105202121177</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6651</v>
+        <v>6534</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>全宇昕</t>
+          <t>正瀚-創</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>596.327139434096</v>
+        <v>596.5304830346231</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>153</v>
+        <v>93</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>52.85462862539603</v>
+        <v>56.377685820084</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>29.15820876787029</v>
+        <v>15.95026664477515</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.5657071327213851</v>
+        <v>1.365323079628226</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>-0.3302301955753322</v>
+        <v>0.3359677804920924</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6693</v>
+        <v>6651</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>廣閎科</t>
+          <t>全宇昕</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>592.7668022939393</v>
+        <v>596.327139434096</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>236.5</v>
+        <v>153</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,13 +2195,13 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>57.38882725730897</v>
+        <v>52.85462862539603</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>48.35219013904855</v>
+        <v>29.15820876787029</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.7093456386997857</v>
+        <v>0.5657071327213851</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>-0.8913554387701943</v>
+        <v>-0.3302301955753322</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6829</v>
+        <v>6693</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>千附精密</t>
+          <t>廣閎科</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>582.0746388788924</v>
+        <v>592.7668022939393</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>222</v>
+        <v>236.5</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,16 +2248,16 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>53.37132264412852</v>
+        <v>57.38882725730897</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>12.80794466052242</v>
+        <v>48.35219013904855</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>1.029161936934242</v>
+        <v>0.7093456386997857</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.134213562158755</v>
+        <v>-0.8913554387701943</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6526</v>
+        <v>6829</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>達發</t>
+          <t>千附精密</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>580.8358868881099</v>
+        <v>582.0746388788924</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>652</v>
+        <v>222</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,29 +2301,29 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>46.55920794044477</v>
+        <v>53.37132264412852</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>12.50977640156015</v>
+        <v>12.80794466052242</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.3180578006867144</v>
+        <v>1.029161936934242</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L35" s="2" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="M35" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-3.836454092270575</v>
+        <v>0.134213562158755</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -2753,21 +2753,21 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6757</v>
+        <v>6641</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>台灣虎航-創</t>
+          <t>基士德-KY</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>539.6201191390852</v>
+        <v>541.3480499949726</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>58.2</v>
+        <v>18.55</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>47.89947150532576</v>
+        <v>52.15916601029208</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>33.4044542250839</v>
+        <v>21.53463700116355</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.3874529482200982</v>
+        <v>0.2348049994972524</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>-0.510026576499796</v>
+        <v>0.0789543981768993</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6556</v>
+        <v>6757</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>勝品</t>
+          <t>台灣虎航-創</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>537.7912947879956</v>
+        <v>539.6201191390852</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>70.59999999999999</v>
+        <v>58.2</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>43.50049532804022</v>
+        <v>47.89947150532576</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>25.4175389739355</v>
+        <v>33.4044542250839</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>4.507926746338204</v>
+        <v>0.3874529482200982</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>-0.193538167136914</v>
+        <v>-0.510026576499796</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6613</v>
+        <v>6556</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>朋億*</t>
+          <t>勝品</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>532.2781759184518</v>
+        <v>537.7912947879956</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>321</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>48.1548853306832</v>
+        <v>43.50049532804022</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>26.18091668333613</v>
+        <v>25.4175389739355</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.3491639708233205</v>
+        <v>4.507926746338204</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-8.294732397284093</v>
+        <v>-0.193538167136914</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6486</v>
+        <v>6668</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>互動</t>
+          <t>中揚光</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>526.4315539908017</v>
+        <v>534.0954600328597</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>83.09999999999999</v>
+        <v>37.9</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,16 +2937,16 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>54.46584108495598</v>
+        <v>44.24061600837763</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>22.52926446869758</v>
+        <v>17.49634825636789</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.7014900816502103</v>
+        <v>0.2315904586944201</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.2434784200002912</v>
+        <v>-0.5166812948567168</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6541</v>
+        <v>6613</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>泰福-KY</t>
+          <t>朋億*</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>520.788563706419</v>
+        <v>532.2781759184518</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>40.8</v>
+        <v>321</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,16 +2990,16 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>50.37825055393518</v>
+        <v>48.1548853306832</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>15.95431463490334</v>
+        <v>26.18091668333613</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.4791819830682827</v>
+        <v>0.3491639708233205</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-0.0515945649777843</v>
+        <v>-8.294732397284093</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6684</v>
+        <v>6669</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>安格</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>513.5871514814752</v>
+        <v>527.7527193266883</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>53.9</v>
+        <v>5040</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,49 +3043,49 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>48.12188760072574</v>
+        <v>51.96524510439431</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>34.74033046096234</v>
+        <v>13.16601854784374</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.2555517275361595</v>
+        <v>1.239935985599949</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L49" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M49" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-0.844057614690052</v>
+        <v>35.82695697358312</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6722</v>
+        <v>6486</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>輝創</t>
+          <t>互動</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>509.7704691092051</v>
+        <v>526.4315539908017</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>35.45</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>41.78422157427065</v>
+        <v>54.46584108495598</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>36.62134005229357</v>
+        <v>22.52926446869758</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.1865728134092482</v>
+        <v>0.7014900816502103</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>0.0319693211539622</v>
+        <v>0.2434784200002912</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, stronger_than_market</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6771</v>
+        <v>6541</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>平和環保-創</t>
+          <t>泰福-KY</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>505.9485006770078</v>
+        <v>520.788563706419</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>39.8</v>
+        <v>40.8</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,16 +3149,16 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>44.11121485010584</v>
+        <v>50.37825055393518</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>20.97283053484768</v>
+        <v>15.95431463490334</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.3808665749470042</v>
+        <v>0.4791819830682827</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>0.0462064449937836</v>
+        <v>-0.0515945649777843</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, stronger_than_market</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6641</v>
+        <v>6684</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>基士德-KY</t>
+          <t>安格</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>501.3480499949725</v>
+        <v>513.5871514814752</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>18.55</v>
+        <v>53.9</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>52.15916601029208</v>
+        <v>48.12188760072574</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>21.53463700116355</v>
+        <v>34.74033046096234</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.2348049994972524</v>
+        <v>0.2555517275361595</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.0789543981768993</v>
+        <v>-0.844057614690052</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6756</v>
+        <v>6722</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>威鋒電子</t>
+          <t>輝創</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>498.5706487819775</v>
+        <v>509.7704691092051</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>99.7</v>
+        <v>35.45</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>51.11622393290391</v>
+        <v>41.78422157427065</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>18.43002931375125</v>
+        <v>36.62134005229357</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.719580924508797</v>
+        <v>0.1865728134092482</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-0.0941166256695159</v>
+        <v>0.0319693211539622</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6805</v>
+        <v>6771</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>平和環保-創</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>498.2261690857841</v>
+        <v>505.9485006770078</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>1460</v>
+        <v>39.8</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,16 +3308,16 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>35.04999473985863</v>
+        <v>44.11121485010584</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>23.31580815943655</v>
+        <v>20.97283053484768</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>1.466381395435663</v>
+        <v>0.3808665749470042</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-27.45016259752049</v>
+        <v>0.0462064449937836</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6530</v>
+        <v>6756</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>創威</t>
+          <t>威鋒電子</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>496.8663280777081</v>
+        <v>498.5706487819775</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>83</v>
+        <v>99.7</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,16 +3361,16 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>35.42061692529114</v>
+        <v>51.11622393290391</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>22.55340177651775</v>
+        <v>18.43002931375125</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.6051592319693341</v>
+        <v>0.719580924508797</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>-0.1612898038329095</v>
+        <v>-0.0941166256695159</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6668</v>
+        <v>6805</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>中揚光</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>494.0954600328597</v>
+        <v>498.2261690857841</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>37.9</v>
+        <v>1460</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>44.24061600837763</v>
+        <v>35.04999473985863</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>17.49634825636789</v>
+        <v>23.31580815943655</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.2315904586944201</v>
+        <v>1.466381395435663</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-0.5166812948567168</v>
+        <v>-27.45016259752049</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6669</v>
+        <v>6530</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>創威</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>487.7527193266883</v>
+        <v>496.8663280777081</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>5040</v>
+        <v>83</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,29 +3467,29 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>51.96524510439431</v>
+        <v>35.42061692529114</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>13.16601854784374</v>
+        <v>22.55340177651775</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>1.239935985599949</v>
+        <v>0.6051592319693341</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L57" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M57" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>35.82695697358312</v>
+        <v>-0.1612898038329095</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
@@ -3548,21 +3548,21 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6691</v>
+        <v>6581</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>洋基工程</t>
+          <t>鋼聯</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>484.1849016766411</v>
+        <v>487.4493408512781</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>708</v>
+        <v>106.5</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>47.83081928113256</v>
+        <v>43.64214916955456</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>26.21879230494516</v>
+        <v>11.34799022438651</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.3184901676641075</v>
+        <v>1.861734772157725</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-8.401246741242378</v>
+        <v>-0.0759752293400259</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6830</v>
+        <v>6691</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>汎銓</t>
+          <t>洋基工程</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>482.9114658730273</v>
+        <v>484.1849016766411</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>416.5</v>
+        <v>708</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>31.57675210294522</v>
+        <v>47.83081928113256</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>25.83060349809814</v>
+        <v>26.21879230494516</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.8696450274370079</v>
+        <v>0.3184901676641075</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-4.110552602012078</v>
+        <v>-8.401246741242378</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6788</v>
+        <v>6830</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>汎銓</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>481.9701892520345</v>
+        <v>482.9114658730273</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>403.5</v>
+        <v>416.5</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,49 +3679,49 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>42.06927033991832</v>
+        <v>31.57675210294522</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>8.618651842756288</v>
+        <v>25.83060349809814</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.4669477995439862</v>
+        <v>0.8696450274370079</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L61" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M61" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-3.771028098114664</v>
+        <v>-4.110552602012078</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, invest_trust_buy_2d, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6614</v>
+        <v>6788</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>資拓宏宇</t>
+          <t>華景電</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>472.1724104726767</v>
+        <v>481.9701892520345</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>40</v>
+        <v>403.5</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,49 +3732,49 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>49.11212072275216</v>
+        <v>42.06927033991832</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>20.77426729531906</v>
+        <v>8.618651842756288</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.4194081595047057</v>
+        <v>0.4669477995439862</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L62" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M62" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.0148271299643166</v>
+        <v>-3.771028098114664</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6581</v>
+        <v>6614</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>鋼聯</t>
+          <t>資拓宏宇</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>467.4493408512781</v>
+        <v>472.1724104726767</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>106.5</v>
+        <v>40</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>43.64214916955456</v>
+        <v>49.11212072275216</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>11.34799022438651</v>
+        <v>20.77426729531906</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>1.861734772157725</v>
+        <v>0.4194081595047057</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>1</v>
@@ -3803,11 +3803,11 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-0.0759752293400259</v>
+        <v>0.0148271299643166</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
@@ -4820,21 +4820,21 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>6725</v>
+        <v>6531</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>矽科宏晟</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>383.5367904348528</v>
+        <v>383.7554484383441</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>305.5</v>
+        <v>922</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,16 +4845,16 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>43.21693973076976</v>
+        <v>44.93989250651241</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>21.50047520525937</v>
+        <v>19.70161541490256</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.1970419132930303</v>
+        <v>0.6913528299949102</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-3.411320418058653</v>
+        <v>-13.47024695107131</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>6561</v>
+        <v>6725</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>是方</t>
+          <t>矽科宏晟</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>381.3219879093637</v>
+        <v>383.5367904348528</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>330.5</v>
+        <v>305.5</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,16 +4898,16 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>39.09196338881269</v>
+        <v>43.21693973076976</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>20.63001740319667</v>
+        <v>21.50047520525937</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.3129231034568797</v>
+        <v>0.1970419132930303</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-0.1680527533914375</v>
+        <v>-3.411320418058653</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>6690</v>
+        <v>6561</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>安碁資訊</t>
+          <t>是方</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>379.4332732063193</v>
+        <v>381.3219879093637</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>166.5</v>
+        <v>330.5</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,16 +4951,16 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>44.63014541075785</v>
+        <v>39.09196338881269</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>14.43662579867491</v>
+        <v>20.63001740319667</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.3219020244547579</v>
+        <v>0.3129231034568797</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-0.3006336229487034</v>
+        <v>-0.1680527533914375</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>6789</v>
+        <v>6690</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>采鈺</t>
+          <t>安碁資訊</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>378.5211467168094</v>
+        <v>379.4332732063193</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>515</v>
+        <v>166.5</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>49.29976006274612</v>
+        <v>44.63014541075785</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>11.45613657085052</v>
+        <v>14.43662579867491</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.5078244177819691</v>
+        <v>0.3219020244547579</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>4</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-0.7010781471795562</v>
+        <v>-0.3006336229487034</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>6597</v>
+        <v>6789</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>立誠</t>
+          <t>采鈺</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>376.4787716480552</v>
+        <v>378.5211467168094</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>67.8</v>
+        <v>515</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,16 +5057,16 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>51.52220358926256</v>
+        <v>49.29976006274612</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>14.4416454967116</v>
+        <v>11.45613657085052</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.2217467632214176</v>
+        <v>0.5078244177819691</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-2.553841087692786</v>
+        <v>-0.7010781471795562</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, williams_r_recovery</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>6715</v>
+        <v>6597</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>嘉基</t>
+          <t>立誠</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>375.7961387345421</v>
+        <v>376.4787716480552</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>391.5</v>
+        <v>67.8</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,16 +5110,16 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>41.02153305558943</v>
+        <v>51.52220358926256</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>17.16508098089622</v>
+        <v>14.4416454967116</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>2.332115911198549</v>
+        <v>0.2217467632214176</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-6.670494945067979</v>
+        <v>-2.553841087692786</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, williams_r_recovery</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>6741</v>
+        <v>6515</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>91APP*-KY</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>375.1821582725876</v>
+        <v>376.1627714219665</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>60</v>
+        <v>7765</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,49 +5163,49 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>40.98150273237917</v>
+        <v>40.32504192944973</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>9.099618418777792</v>
+        <v>15.73228471199892</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>1.474235345176557</v>
+        <v>0.7537787896570529</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L89" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M89" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-0.1252753070053037</v>
+        <v>-129.3450513143999</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>6510</v>
+        <v>6715</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>嘉基</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>372.8793682236349</v>
+        <v>375.7961387345421</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>2855</v>
+        <v>391.5</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,49 +5216,49 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>37.5037168934422</v>
+        <v>41.02153305558943</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>20.50776648792229</v>
+        <v>17.16508098089622</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.6169599725795567</v>
+        <v>2.332115911198549</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L90" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M90" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-53.90204377594968</v>
+        <v>-6.670494945067979</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>6763</v>
+        <v>6741</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>綠界科技</t>
+          <t>91APP*-KY</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>372.2888543904213</v>
+        <v>375.1821582725876</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>45.9</v>
+        <v>60</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,16 +5269,16 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>44.24551976832949</v>
+        <v>40.98150273237917</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>14.3906360408211</v>
+        <v>9.099618418777792</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.7669989018105312</v>
+        <v>1.474235345176557</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-0.1506834430244326</v>
+        <v>-0.1252753070053037</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>6640</v>
+        <v>6510</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>均華</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>366.708003289398</v>
+        <v>372.8793682236349</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>995</v>
+        <v>2855</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,49 +5322,49 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>38.78904336163709</v>
+        <v>37.5037168934422</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>19.61234233846608</v>
+        <v>20.50776648792229</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.6161250987838414</v>
+        <v>0.6169599725795567</v>
       </c>
       <c r="K92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L92" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L92" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M92" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>2.992810436708212</v>
+        <v>-53.90204377594968</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>6588</v>
+        <v>6763</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>東典光電</t>
+          <t>綠界科技</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>365.7707035167654</v>
+        <v>372.2888543904213</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>78.90000000000001</v>
+        <v>45.9</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>27.44225560475532</v>
+        <v>44.24551976832949</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>21.34932604040345</v>
+        <v>14.3906360408211</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.5217914986181071</v>
+        <v>0.7669989018105312</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-0.6701959009609251</v>
+        <v>-0.1506834430244326</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>6667</v>
+        <v>6640</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>信紘科</t>
+          <t>均華</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>363.4068678810371</v>
+        <v>366.708003289398</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>255</v>
+        <v>995</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,16 +5428,16 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>40.36420614039848</v>
+        <v>38.78904336163709</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>11.25283339005108</v>
+        <v>19.61234233846608</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.326947522433445</v>
+        <v>0.6161250987838414</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-2.09710506603584</v>
+        <v>2.992810436708212</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>6695</v>
+        <v>6588</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>芯鼎</t>
+          <t>東典光電</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>354.5040666521084</v>
+        <v>365.7707035167654</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>53.7</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>44.25081250665493</v>
+        <v>27.44225560475532</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>20.01410549803342</v>
+        <v>21.34932604040345</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.2781308503205539</v>
+        <v>0.5217914986181071</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-1.002137708427648</v>
+        <v>-0.6701959009609251</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>6768</v>
+        <v>6667</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>志強-KY</t>
+          <t>信紘科</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>351.2708120455608</v>
+        <v>363.4068678810371</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>71.2</v>
+        <v>255</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,16 +5534,16 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>26.43697351487201</v>
+        <v>40.36420614039848</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>28.28702706409566</v>
+        <v>11.25283339005108</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.5996688685354499</v>
+        <v>0.326947522433445</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-1.143813432097494</v>
+        <v>-2.09710506603584</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>6689</v>
+        <v>6695</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>伊雲谷</t>
+          <t>芯鼎</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>344.0970528510371</v>
+        <v>354.5040666521084</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>63.8</v>
+        <v>53.7</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,16 +5587,16 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>41.37266848906904</v>
+        <v>44.25081250665493</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>15.33572375315994</v>
+        <v>20.01410549803342</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.3667007007287019</v>
+        <v>0.2781308503205539</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-0.0371268968194189</v>
+        <v>-1.002137708427648</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>6531</v>
+        <v>6768</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>志強-KY</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>343.755448438344</v>
+        <v>351.2708120455608</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>922</v>
+        <v>71.2</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,16 +5640,16 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>44.93989250651241</v>
+        <v>26.43697351487201</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>19.70161541490256</v>
+        <v>28.28702706409566</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.6913528299949102</v>
+        <v>0.5996688685354499</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-13.47024695107131</v>
+        <v>-1.143813432097494</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>6584</v>
+        <v>6689</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>南俊國際</t>
+          <t>伊雲谷</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>341.5014138720194</v>
+        <v>344.0970528510371</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>663</v>
+        <v>63.8</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,16 +5693,16 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>48.49963351571066</v>
+        <v>41.37266848906904</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>13.68941483089875</v>
+        <v>15.33572375315994</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.250640185268231</v>
+        <v>0.3667007007287019</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-1.546796010479504</v>
+        <v>-0.0371268968194189</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>6515</v>
+        <v>6584</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>南俊國際</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>336.1627714219665</v>
+        <v>341.5014138720194</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>7765</v>
+        <v>663</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,29 +5746,29 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>40.32504192944973</v>
+        <v>48.49963351571066</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>15.73228471199892</v>
+        <v>13.68941483089875</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.7537787896570529</v>
+        <v>0.250640185268231</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L100" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M100" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-129.3450513143999</v>
+        <v>-1.546796010479504</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, dealer_buy_3d</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -6304,21 +6304,21 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>6761</v>
+        <v>6533</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>穩得</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>265.8147523292832</v>
+        <v>271.019284031169</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>181</v>
+        <v>191.5</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>42.60938299468615</v>
+        <v>39.34478541705536</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>12.64427604056821</v>
+        <v>9.453825813729642</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.9961010342967304</v>
+        <v>0.4116433795171787</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-0.9036602854693992</v>
+        <v>0.06783734416913841</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>6498</v>
+        <v>6761</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>久禾光</t>
+          <t>穩得</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>261.1769073280221</v>
+        <v>265.8147523292832</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>91.8</v>
+        <v>181</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,16 +6382,16 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>41.4882705419237</v>
+        <v>42.60938299468615</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>18.97596249194498</v>
+        <v>12.64427604056821</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.3255869692953529</v>
+        <v>0.9961010342967304</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-0.9173587365460693</v>
+        <v>-0.9036602854693992</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>6605</v>
+        <v>6498</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>帝寶</t>
+          <t>久禾光</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>255.499487966438</v>
+        <v>261.1769073280221</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>126</v>
+        <v>91.8</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>33.57567588141866</v>
+        <v>41.4882705419237</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>13.53493576345398</v>
+        <v>18.97596249194498</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>2.449948796643803</v>
+        <v>0.3255869692953529</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>1</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-1.289102728643541</v>
+        <v>-0.9173587365460693</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>6533</v>
+        <v>6605</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>帝寶</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>251.019284031169</v>
+        <v>255.499487966438</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>191.5</v>
+        <v>126</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,16 +6488,16 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>39.34478541705536</v>
+        <v>33.57567588141866</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>9.453825813729642</v>
+        <v>13.53493576345398</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.4116433795171787</v>
+        <v>2.449948796643803</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>0.06783734416913841</v>
+        <v>-1.289102728643541</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>6558</v>
+        <v>6643</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>興能高</t>
+          <t>M31</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>248.1066860659051</v>
+        <v>246.7443182003722</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>29.8</v>
+        <v>442</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,16 +6541,16 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>46.94589364220873</v>
+        <v>35.73910293436239</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>16.41761503232766</v>
+        <v>18.79145957529873</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.4195210839764871</v>
+        <v>1.104121604883709</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L115" s="2" t="n">
         <v>0</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>0.0660881360678495</v>
+        <v>-0.1686557511894655</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>6674</v>
+        <v>6692</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>鋐寶科技</t>
+          <t>進能服</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>247.3706975194452</v>
+        <v>246.6309442467248</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>16.8</v>
+        <v>25</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,13 +6594,13 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>40.38139183846709</v>
+        <v>41.72174719942128</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>18.13934322261268</v>
+        <v>12.54193452547294</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.4983078002169389</v>
+        <v>0.2419352251399605</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>0</v>
@@ -6612,7 +6612,7 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-0.0226857405212607</v>
+        <v>0.0209835230382586</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
@@ -6622,21 +6622,21 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>6643</v>
+        <v>6803</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>M31</t>
+          <t>崑鼎</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>246.7443182003722</v>
+        <v>239.9642073391053</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>442</v>
+        <v>274</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,16 +6647,16 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>35.73910293436239</v>
+        <v>28.53793049864439</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>18.79145957529873</v>
+        <v>36.65968903144845</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>1.104121604883709</v>
+        <v>0.2369421464651919</v>
       </c>
       <c r="K117" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L117" s="2" t="n">
         <v>0</v>
@@ -6665,31 +6665,31 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>-0.1686557511894655</v>
+        <v>-1.579237518361683</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>6692</v>
+        <v>6532</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>進能服</t>
+          <t>瑞耘</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>246.6309442467248</v>
+        <v>237.9545737167573</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>25</v>
+        <v>78</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,16 +6700,16 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>41.72174719942128</v>
+        <v>31.24913595285118</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>12.54193452547294</v>
+        <v>16.1545400091649</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.2419352251399605</v>
+        <v>0.7762651967701159</v>
       </c>
       <c r="K118" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L118" s="2" t="n">
         <v>0</v>
@@ -6718,31 +6718,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>0.0209835230382586</v>
+        <v>-0.9832574008631489</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>6803</v>
+        <v>6807</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>崑鼎</t>
+          <t>峰源-KY</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>239.9642073391053</v>
+        <v>224.0150085429477</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>274</v>
+        <v>33.35</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,16 +6753,16 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>28.53793049864439</v>
+        <v>46.52416976153248</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>36.65968903144845</v>
+        <v>13.95221314332964</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.2369421464651919</v>
+        <v>0.333634743756815</v>
       </c>
       <c r="K119" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L119" s="2" t="n">
         <v>0</v>
@@ -6771,31 +6771,31 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>-1.579237518361683</v>
+        <v>0.07533203571149159</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>6532</v>
+        <v>6546</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>瑞耘</t>
+          <t>正基</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>237.9545737167573</v>
+        <v>223.4927247787704</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>78</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,13 +6806,13 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>31.24913595285118</v>
+        <v>40.83189033534597</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>16.1545400091649</v>
+        <v>13.29868819812367</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.7762651967701159</v>
+        <v>0.752247196514949</v>
       </c>
       <c r="K120" s="2" t="n">
         <v>1</v>
@@ -6824,7 +6824,7 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>-0.9832574008631489</v>
+        <v>-0.3719280812801768</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
@@ -6834,21 +6834,21 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>6591</v>
+        <v>6558</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>動力-KY</t>
+          <t>興能高</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>231.8795914127692</v>
+        <v>218.1066860659051</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>49.4</v>
+        <v>29.8</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,16 +6859,16 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>31.54900827599663</v>
+        <v>46.94589364220873</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>22.90409423219014</v>
+        <v>16.41761503232766</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>1.305711264294257</v>
+        <v>0.4195210839764871</v>
       </c>
       <c r="K121" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L121" s="2" t="n">
         <v>0</v>
@@ -6877,31 +6877,31 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>-0.4216307764317983</v>
+        <v>0.0660881360678495</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>6807</v>
+        <v>6674</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>峰源-KY</t>
+          <t>鋐寶科技</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>224.0150085429477</v>
+        <v>217.3706975194452</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>33.35</v>
+        <v>16.8</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,13 +6912,13 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>46.52416976153248</v>
+        <v>40.38139183846709</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>13.95221314332964</v>
+        <v>18.13934322261268</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.333634743756815</v>
+        <v>0.4983078002169389</v>
       </c>
       <c r="K122" s="2" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>0.07533203571149159</v>
+        <v>-0.0226857405212607</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
@@ -6940,21 +6940,21 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>6546</v>
+        <v>6680</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>正基</t>
+          <t>鑫創電子</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>223.4927247787704</v>
+        <v>215.1806078656739</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>67.59999999999999</v>
+        <v>49.35</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6965,16 +6965,16 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>40.83189033534597</v>
+        <v>50.04762709247905</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>13.29868819812367</v>
+        <v>3.979599990881894</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.752247196514949</v>
+        <v>0.0916956364419161</v>
       </c>
       <c r="K123" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L123" s="2" t="n">
         <v>0</v>
@@ -6983,31 +6983,31 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>-0.3719280812801768</v>
+        <v>0.0930235033627497</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>6680</v>
+        <v>6706</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>鑫創電子</t>
+          <t>惠特</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>215.1806078656739</v>
+        <v>211.513259131728</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>49.35</v>
+        <v>139</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7018,13 +7018,13 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>50.04762709247905</v>
+        <v>37.54028330554185</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>3.979599990881894</v>
+        <v>16.35562291396795</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.0916956364419161</v>
+        <v>0.2773792467241036</v>
       </c>
       <c r="K124" s="2" t="n">
         <v>0</v>
@@ -7036,31 +7036,31 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>0.0930235033627497</v>
+        <v>-1.519361429137161</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>6706</v>
+        <v>6591</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>惠特</t>
+          <t>動力-KY</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v/>
       </c>
       <c r="D125" s="2" t="n">
-        <v>211.513259131728</v>
+        <v>201.8795914127692</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>139</v>
+        <v>49.4</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
@@ -7071,13 +7071,13 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>37.54028330554185</v>
+        <v>31.54900827599663</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>16.35562291396795</v>
+        <v>22.90409423219014</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>0.2773792467241036</v>
+        <v>1.305711264294257</v>
       </c>
       <c r="K125" s="2" t="n">
         <v>0</v>
@@ -7089,31 +7089,31 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>-1.519361429137161</v>
+        <v>-0.4216307764317983</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>6552</v>
+        <v>6754</v>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>易華電</t>
+          <t>匯僑設計</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
         <v/>
       </c>
       <c r="D126" s="2" t="n">
-        <v>180.7910911011637</v>
+        <v>179.8881303456991</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>29.45</v>
+        <v>41.5</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -7124,16 +7124,16 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>45.23529014758144</v>
+        <v>31.97657396369875</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>11.04092161165751</v>
+        <v>18.93448359424568</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>0.6252321844502756</v>
+        <v>0.5416796400835713</v>
       </c>
       <c r="K126" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L126" s="2" t="n">
         <v>0</v>
@@ -7142,31 +7142,31 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>-0.08376396779094911</v>
+        <v>-0.398411468954379</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>6754</v>
+        <v>6552</v>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>匯僑設計</t>
+          <t>易華電</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
         <v/>
       </c>
       <c r="D127" s="2" t="n">
-        <v>179.8881303456991</v>
+        <v>150.7910911011637</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>41.5</v>
+        <v>29.45</v>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
@@ -7177,16 +7177,16 @@
         <v>0</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>31.97657396369875</v>
+        <v>45.23529014758144</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>18.93448359424568</v>
+        <v>11.04092161165751</v>
       </c>
       <c r="J127" s="2" t="n">
-        <v>0.5416796400835713</v>
+        <v>0.6252321844502756</v>
       </c>
       <c r="K127" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L127" s="2" t="n">
         <v>0</v>
@@ -7195,11 +7195,11 @@
         <v>-1</v>
       </c>
       <c r="N127" s="2" t="n">
-        <v>-0.398411468954379</v>
+        <v>-0.08376396779094911</v>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
